--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Philosophes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mode_d_emploi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Philosophes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode_d_emploi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="L14" s="28" t="inlineStr">
         <is>
-          <t>poète lyrique et penseur politique russe, grandes voix de la poésie russe et théoricien du panslavisme.</t>
+          <t>poète lyrique et penseur politique russe, l'une des grandes voix de la poésie russe et théoricien du panslavisme.</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
-          <t>philosophe russe et l'un des fondateur du mouvement slavophile.</t>
+          <t>philosophe russe et l'un des fondateurs du mouvement slavophile.</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="L37" s="19" t="inlineStr">
         <is>
-          <t>philosophe et ésotériste russe cofondatrice du Théosophisme.</t>
+          <t>philosophe et ésotériste russe cofondatrice de la théosophie.</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="L40" s="19" t="inlineStr">
         <is>
-          <t>philosophe et critique russe, l’un des plus radical du nihilisme russe.</t>
+          <t>philosophe et critique russe, l’un des plus radicaux du nihilisme russe.</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L54" s="19" t="inlineStr">
         <is>
-          <t>philosophe et écrivain russe radicalement anti-systèmatique.</t>
+          <t>philosophe et écrivain russe radicalement antisystématique.</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="L65" s="19" t="inlineStr">
         <is>
-          <t>philosophe et économiste russe, figure de la philosophique religieuse russe.</t>
+          <t>philosophe et économiste russe, figure de la philosophie religieuse russe.</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="L78" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe et diplomate russe du cosmisme ou il développa une réflexion sur le temps et la maîtrise humaine du cosmos.</t>
+          <t xml:space="preserve"> philosophe et diplomate russe du cosmisme, où il développa une réflexion sur le temps et la maîtrise humaine du cosmos.</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="L84" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">théologien orthodoxe russe qui appelé à un retour aux Pères de l’Église et à une « synthèse néo-patristique » contre les influences occidentales. </t>
+          <t xml:space="preserve">théologien orthodoxe russe qui appela à un retour aux Pères de l’Église et à une « synthèse néo-patristique » contre les influences occidentales. </t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -4472,7 +4472,7 @@
       </c>
       <c r="L77" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe russe, représentant du courant de l'intuitivisme réaliste.</t>
+          <t>philosophe russe de l'intuitivisme réaliste, proche de Lossky, penseur de la logique et de la connaissance.</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="L79" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe russe, représentant du courant de l'intuitivisme réaliste.</t>
+          <t>philosophe russe, disciple de Lossky, défenseur d'une perception directe du réel, mort en 1920.</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -638,6 +638,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="186.75" customHeight="1" s="20">
       <c r="A4" s="18" t="n">
@@ -3593,6 +3598,11 @@
           <t xml:space="preserve"> philosophe russe, représentant de l'existentialisme religieux et de la pensée irrationnaliste européenne.</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="90.25" customHeight="1" s="20">
       <c r="A61" s="18" t="n">
@@ -4056,6 +4066,11 @@
           <t xml:space="preserve"> philosophe russe d'origine juive, représentant de la philosophie religieuse russe.</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="261.15" customHeight="1" s="20">
       <c r="A70" s="18" t="n">
@@ -4162,6 +4177,11 @@
           <t>révolutionnaire, théoricien marxiste et homme d'État russe, figure majeure du mouvement communiste international.</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="289.55" customHeight="1" s="20">
       <c r="A72" s="18" t="n">
@@ -4980,6 +5000,11 @@
           <t>psychologue et philosophe soviétique, figure de la psychologie du développement et de la philosophie de l'éducation.</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="285.05" customHeight="1" s="20">
       <c r="A88" s="18" t="n">
@@ -5033,6 +5058,11 @@
           <t xml:space="preserve"> logicienne et philosophe soviétique, pionnière de la logique mathématique et figure du matérialisme dialectique.</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="326.85" customHeight="1" s="20">
       <c r="A89" s="18" t="n">
@@ -5185,6 +5215,11 @@
       <c r="L91" s="19" t="inlineStr">
         <is>
           <t>philosophe, esthéticien et critique d'art marxiste soviétique.</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -643,6 +643,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="186.75" customHeight="1" s="20">
       <c r="A4" s="18" t="n">
@@ -697,6 +707,11 @@
           <t>philosophe et poète russe, l'une des figures les plus remarquables des Lumières russes.</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="177.75" customHeight="1" s="20">
       <c r="A5" s="18" t="n">
@@ -751,6 +766,11 @@
           <t>philosophe et poète ukrainien fondateur de l'espace culturel slavo-oriental.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="203.25" customHeight="1" s="20">
       <c r="A6" s="18" t="n">
@@ -805,6 +825,11 @@
           <t>philosophe et homme d'État russe, figure majeure des Lumières russes du XVIIIe.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="225.75" customHeight="1" s="20">
       <c r="A7" s="18" t="n">
@@ -859,6 +884,11 @@
           <t>philosophe et philanthrope des Lumières russes et du mysticisme maçonnique.</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="168.75" customHeight="1" s="20">
       <c r="A8" s="18" t="n">
@@ -913,6 +943,11 @@
           <t>philosophe russe représentant de la pensée libérale et critique en Russie.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="299.25" customHeight="1" s="20">
       <c r="A9" s="18" t="n">
@@ -967,6 +1002,11 @@
           <t>philosophe et grand réformateur russe du règne d'Alexandre Ier.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="270.85" customHeight="1" s="20">
       <c r="A10" s="18" t="n">
@@ -1021,6 +1061,14 @@
           <t xml:space="preserve">philosophe russe, auteur des célèbres &lt;em&gt;Lettres philosophiques&lt;/em&gt;, qui déclencha un scandale intellectuel. </t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" ht="187.5" customHeight="1" s="20">
       <c r="A11" s="18" t="n">
@@ -1075,6 +1123,16 @@
           <t>philosophe polonais et la figure la plus emblématique du romantisme polonais.</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="250.7" customHeight="1" s="20">
       <c r="A12" s="18" t="n">
@@ -1123,6 +1181,11 @@
           <t>philosophe russe, figure importante de la philosophie académique chrétienne orthodoxe.</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="279.1" customHeight="1" s="20">
       <c r="A13" s="18" t="n">
@@ -1171,6 +1234,11 @@
           <t>philosophe, écrivain et musicologue russe du mouvement romantique.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="92.25" customHeight="1" s="20">
       <c r="A14" s="18" t="n">
@@ -1219,6 +1287,11 @@
           <t>poète lyrique et penseur politique russe, l'une des grandes voix de la poésie russe et théoricien du panslavisme.</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="189.75" customHeight="1" s="20">
       <c r="A15" s="18" t="n">
@@ -1272,6 +1345,14 @@
           <t>philosophe russe, cofondateur du mouvement slavophile.</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" ht="195.75" customHeight="1" s="20">
       <c r="A16" s="18" t="n">
@@ -1325,6 +1406,11 @@
           <t>philosophe russe et l'un des fondateurs du mouvement slavophile.</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="280.55" customHeight="1" s="20">
       <c r="A17" s="18" t="n">
@@ -1378,6 +1464,11 @@
           <t>philosophe russe figure de proue de l'intelligentsia progressiste des années 1840.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="193.5" customHeight="1" s="20">
       <c r="A18" s="18" t="n">
@@ -1432,6 +1523,14 @@
           <t>philosophe russe figure de l'intelligentsia libérale et socialiste russe.</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O18">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" ht="186.75" customHeight="1" s="20">
       <c r="A19" s="18" t="n">
@@ -1485,6 +1584,11 @@
           <t>philosophe, poète et animateur culturel russe, fondateur du célèbre Cercle Stankevitch.</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="240" customHeight="1" s="20">
       <c r="A20" s="18" t="n">
@@ -1540,6 +1644,14 @@
           <t>philosophe, théoricien politique et révolutionnaire russe, figure de l'anarchisme.</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" ht="75.34999999999999" customHeight="1" s="20">
       <c r="A21" s="18" t="n">
@@ -1593,6 +1705,11 @@
           <t>philosophe russe et l'un des principaux théoriciens du slavophilisme.</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="82.8" customHeight="1" s="20">
       <c r="A22" s="18" t="n">
@@ -1646,6 +1763,11 @@
           <t>philosophe social russe, l'une des figures fondatrices de l'occidentalisme libéral.</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="89.55" customHeight="1" s="20">
       <c r="A23" s="18" t="n">
@@ -1699,6 +1821,14 @@
           <t>romancier et penseur russe, figure de la littérature mondiale.</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" ht="201.45" customHeight="1" s="20">
       <c r="A24" s="18" t="n">
@@ -1753,6 +1883,11 @@
           <t>philosophe naturaliste russe, auteur d'une théorie sur le relativisme civilisationnel.</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="70.84999999999999" customHeight="1" s="20">
       <c r="A25" s="18" t="n">
@@ -1806,6 +1941,11 @@
           <t>philosophe et poète russe principal représentant du slavophilisme.</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="316.4" customHeight="1" s="20">
       <c r="A26" s="18" t="n">
@@ -1859,6 +1999,11 @@
           <t>philosophe russe du mouvement populiste et de la pensée socialiste russe.</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="296.25" customHeight="1" s="20">
       <c r="A27" s="18" t="n">
@@ -1912,6 +2057,11 @@
           <t>philosophe russe spécialiste de la philosophie chrétienne orthodoxe.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="126.85" customHeight="1" s="20">
       <c r="A28" s="18" t="n">
@@ -1965,6 +2115,11 @@
           <t>philosophe et homme d’état russe symbole de la réaction contre les réformes libérales des années 1860-1870.</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="232.05" customHeight="1" s="20">
       <c r="A29" s="18" t="n">
@@ -2019,6 +2174,11 @@
           <t xml:space="preserve"> philosophe et révolutionnaire russe, figure centrale du courant nihiliste et matérialiste. </t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="246.25" customHeight="1" s="20">
       <c r="A30" s="18" t="n">
@@ -2072,6 +2232,11 @@
           <t>philosophe et naturaliste russe qui chercha à enraciner la pensée russe dans les valeurs organiques du peuple.</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="98.5" customHeight="1" s="20">
       <c r="A31" s="18" t="n">
@@ -2125,6 +2290,14 @@
           <t>romancier, moraliste et penseur anarchiste russe, l'un des plus grands écrivains de la littérature mondiale.</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" ht="278.35" customHeight="1" s="20">
       <c r="A32" s="18" t="n">
@@ -2173,6 +2346,14 @@
           <t>philosophe et théologien russe représentant de la philosophie chrétienne orthodoxe.</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" ht="305.2" customHeight="1" s="20">
       <c r="A33" s="18" t="n">
@@ -2221,6 +2402,11 @@
           <t>philosophe et juriste russe représentant du libéralisme philosophique russe.</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="261.15" customHeight="1" s="20">
       <c r="A34" s="18" t="n">
@@ -2274,6 +2460,14 @@
           <t xml:space="preserve"> philosophe russe excentrique et visionnaire, fondateur du cosmisme russe.</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O34">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" ht="304.45" customHeight="1" s="20">
       <c r="A35" s="18" t="n">
@@ -2322,6 +2516,11 @@
           <t>physiologiste et philosophe matérialiste russe, fondateur de la physiologie scientifique.</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="273.1" customHeight="1" s="20">
       <c r="A36" s="18" t="n">
@@ -2375,6 +2574,11 @@
           <t>philosophe  et diplomate russe qui développa une philosophie conservatrice d’une originalité radicale.</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="305.2" customHeight="1" s="20">
       <c r="A37" s="18" t="n">
@@ -2428,6 +2632,16 @@
           <t>philosophe et ésotériste russe cofondatrice de la théosophie.</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="71.59999999999999" customHeight="1" s="20">
       <c r="A38" s="18" t="n">
@@ -2476,6 +2690,11 @@
           <t>philosophe russe pionnier du personnalisme philosophique en Russie.</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="67.15000000000001" customHeight="1" s="20">
       <c r="A39" s="18" t="n">
@@ -2529,6 +2748,11 @@
           <t>philosophe russe-allemand qui analyse épistémologiquement la structure de la connaissance humaine.</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="246.25" customHeight="1" s="20">
       <c r="A40" s="18" t="n">
@@ -2582,6 +2806,11 @@
           <t>philosophe et critique russe, l’un des plus radicaux du nihilisme russe.</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="270.1" customHeight="1" s="20">
       <c r="A41" s="18" t="n">
@@ -2630,6 +2859,11 @@
           <t>philosophe et logicien russe pionnier de la logique moderne en Russie.</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="282.05" customHeight="1" s="20">
       <c r="A42" s="18" t="n">
@@ -2683,6 +2917,14 @@
           <t>philosophe russe et figure majeure du mouvement anarchiste international.</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" ht="232.05" customHeight="1" s="20">
       <c r="A43" s="18" t="n">
@@ -2736,6 +2978,11 @@
           <t>philosophe et théoricien du populisme russe et figure dominante du journalisme progressiste.</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55.95" customHeight="1" s="20">
       <c r="A44" s="18" t="n">
@@ -2784,6 +3031,11 @@
           <t>philosophe idéaliste russe dans le courant de l'idéalisme spéculatif.</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="61.15" customHeight="1" s="20">
       <c r="A45" s="18" t="n">
@@ -2832,6 +3084,16 @@
           <t xml:space="preserve"> philosophe positiviste russo-français pionnier de la sociologie scientifique.</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="77.59999999999999" customHeight="1" s="20">
       <c r="A46" s="18" t="n">
@@ -2880,6 +3142,11 @@
           <t>philosophe russe, représentant du courant slavophile et du personnalisme chrétien.</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="61.15" customHeight="1" s="20">
       <c r="A47" s="18" t="n">
@@ -2933,6 +3200,11 @@
           <t>révolutionnaire, théoricien du terrorisme et figure du nihilisme russe.</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="273.85" customHeight="1" s="20">
       <c r="A48" s="18" t="n">
@@ -2986,6 +3258,11 @@
           <t xml:space="preserve"> historien et philosophe russe, fondateur de la science historique moderne russe.</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="341.75" customHeight="1" s="20">
       <c r="A49" s="18" t="n">
@@ -3034,6 +3311,11 @@
           <t>philosophe et psychologue russe, fondateur de la principale revue philosophique russe de son époque.</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="261.15" customHeight="1" s="20">
       <c r="A50" s="18" t="n">
@@ -3087,6 +3369,14 @@
           <t xml:space="preserve"> philosophe, poète et théologien russe, figure de la philosophie religieuse du XIXe.</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O50">
+        <v>3</v>
+      </c>
     </row>
     <row r="51" ht="261.9" customHeight="1" s="20">
       <c r="A51" s="18" t="n">
@@ -3135,6 +3425,11 @@
           <t xml:space="preserve"> philosophe du droit russe,  penseur de la philosophie juridique russe.</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="291" customHeight="1" s="20">
       <c r="A52" s="18" t="n">
@@ -3188,6 +3483,11 @@
           <t>Philosophe russe représentant du spiritualisme et du personnalisme philosophique.</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="288.05" customHeight="1" s="20">
       <c r="A53" s="18" t="n">
@@ -3236,6 +3536,11 @@
           <t>penseur et poète helléniste,  figure  du symbolisme russe.</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="231.3" customHeight="1" s="20">
       <c r="A54" s="18" t="n">
@@ -3289,6 +3594,11 @@
           <t>philosophe et écrivain russe radicalement antisystématique.</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="280.55" customHeight="1" s="20">
       <c r="A55" s="18" t="n">
@@ -3342,6 +3652,11 @@
           <t>philosophe et théoricien politique  révolutionnaire, reconnu comme le père du marxisme russe.</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="250" customHeight="1" s="20">
       <c r="A56" s="18" t="n">
@@ -3390,6 +3705,11 @@
           <t>Cosmisme</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="310.4" customHeight="1" s="20">
       <c r="A57" s="18" t="n">
@@ -3438,6 +3758,11 @@
           <t xml:space="preserve">philosophe, historien de la philosophie ancienne, figure de la renaissance philosophique religieuse russe. </t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="361.9" customHeight="1" s="20">
       <c r="A58" s="18" t="n">
@@ -3491,6 +3816,11 @@
           <t xml:space="preserve"> naturaliste, géochimiste et philosophe russe, père des concepts de biosphère et de noosphère.</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="361.9" customHeight="1" s="20">
       <c r="A59" s="18" t="n">
@@ -3545,6 +3875,11 @@
           <t>philosophe russe religieux et libéral qui a cherché à unir la pensée chrétienne.</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="282.8" customHeight="1" s="20">
       <c r="A60" s="18" t="n">
@@ -3603,6 +3938,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O60">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" ht="90.25" customHeight="1" s="20">
       <c r="A61" s="18" t="n">
@@ -3656,6 +3999,11 @@
           <t>poète, philosophe et théoricien, figure  importante du symbolisme russe.</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="296.25" customHeight="1" s="20">
       <c r="A62" s="18" t="n">
@@ -3704,6 +4052,16 @@
           <t xml:space="preserve"> philosophe et bouddhiste russe, fondateur de l'école russo-soviétique des études bouddhistes.</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inde</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="151.45" customHeight="1" s="20">
       <c r="A63" s="18" t="n">
@@ -3758,6 +4116,11 @@
           <t xml:space="preserve"> philosophe et juriste russe-polonais connu pour avoir élaboré une « théorie psychologique du droit ».</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="118.65" customHeight="1" s="20">
       <c r="A64" s="18" t="n">
@@ -3801,6 +4164,14 @@
           <t>philosophe russe, fondateur de l'intuitivisme  russe et représentant du personnalisme chrétien.</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O64">
+        <v>2</v>
+      </c>
     </row>
     <row r="65" ht="288.8" customHeight="1" s="20">
       <c r="A65" s="18" t="n">
@@ -3854,6 +4225,11 @@
           <t>philosophe et économiste russe, figure de la philosophie religieuse russe.</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="244.75" customHeight="1" s="20">
       <c r="A66" s="18" t="n">
@@ -3907,6 +4283,11 @@
           <t>philosophe, médecin, économiste et théoricien politique russe, figure centrale et marginalisée de la pensée révolutionnaire.</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="58.95" customHeight="1" s="20">
       <c r="A67" s="18" t="n">
@@ -3960,6 +4341,11 @@
           <t>penseur,  écrivain et théoricien russe, fondateur du mouvement symboliste russe.</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="205.2" customHeight="1" s="20">
       <c r="A68" s="18" t="n">
@@ -4013,6 +4399,14 @@
           <t xml:space="preserve"> philosophe russe et figure de la philosophie chrétienne et existentialiste.</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O68">
+        <v>3</v>
+      </c>
     </row>
     <row r="69" ht="282.8" customHeight="1" s="20">
       <c r="A69" s="18" t="n">
@@ -4071,6 +4465,14 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" ht="261.15" customHeight="1" s="20">
       <c r="A70" s="18" t="n">
@@ -4124,6 +4526,11 @@
           <t>philosophe, mathématicien et ésotériste russe, principal diffuseur de l'enseignement de Gurdjieff en Occident.</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="302.95" customHeight="1" s="20">
       <c r="A71" s="18" t="n">
@@ -4182,6 +4589,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="289.55" customHeight="1" s="20">
       <c r="A72" s="18" t="n">
@@ -4235,6 +4647,11 @@
           <t xml:space="preserve">penseur et  poète russe, figure  emblématique du symbolisme russe. </t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="71.59999999999999" customHeight="1" s="20">
       <c r="A73" s="18" t="n">
@@ -4288,6 +4705,11 @@
           <t>romancier, poète, philosophe et théoricien du symbolisme russe.</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="259.7" customHeight="1" s="20">
       <c r="A74" s="18" t="n">
@@ -4341,6 +4763,14 @@
           <t xml:space="preserve"> prêtre orthodoxe, philosophe, mathématicien et théologien russe, figure  de la culture russe du XXe siècle.</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O74">
+        <v>3</v>
+      </c>
     </row>
     <row r="75" ht="290.25" customHeight="1" s="20">
       <c r="A75" s="18" t="n">
@@ -4394,6 +4824,11 @@
           <t>théoricien anarchiste et révolutionnaire russe, représentant de l'anarchisme-communisme.</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="310.4" customHeight="1" s="20">
       <c r="A76" s="18" t="n">
@@ -4447,6 +4882,11 @@
           <t>philosophe, théologien et publiciste politique russe, penseur du conservatisme et du nationalisme russe.</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="244" customHeight="1" s="20">
       <c r="A77" s="18" t="n">
@@ -4495,6 +4935,11 @@
           <t>philosophe russe de l'intuitivisme réaliste, proche de Lossky, penseur de la logique et de la connaissance.</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="217.9" customHeight="1" s="20">
       <c r="A78" s="18" t="n">
@@ -4548,6 +4993,11 @@
           <t xml:space="preserve"> philosophe et diplomate russe du cosmisme, où il développa une réflexion sur le temps et la maîtrise humaine du cosmos.</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="261.15" customHeight="1" s="20">
       <c r="A79" s="18" t="n">
@@ -4596,6 +5046,11 @@
           <t>philosophe russe, disciple de Lossky, défenseur d'une perception directe du réel, mort en 1920.</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="304.45" customHeight="1" s="20">
       <c r="A80" s="18" t="n">
@@ -4644,6 +5099,11 @@
           <t xml:space="preserve"> philosophe, poète et théologien russe, figure intéressante du cosmisme.</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="246.25" customHeight="1" s="20">
       <c r="A81" s="18" t="n">
@@ -4692,6 +5152,11 @@
           <t>philosophe et cosmiste russe, principal diffuseur de la pensée de Nikolaï Fedorov.</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="80.55" customHeight="1" s="20">
       <c r="A82" s="18" t="n">
@@ -4740,6 +5205,11 @@
           <t>orientaliste, japonologue et philosophe de la culture russe et soviétique.</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="317.9" customHeight="1" s="20">
       <c r="A83" s="18" t="n">
@@ -4788,6 +5258,11 @@
           <t>philosophe et historien de la philosophie russe, représentant du courant de l'intuitivisme réaliste.</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="318.65" customHeight="1" s="20">
       <c r="A84" s="18" t="n">
@@ -4841,6 +5316,11 @@
           <t xml:space="preserve">théologien orthodoxe russe qui appela à un retour aux Pères de l’Église et à une « synthèse néo-patristique » contre les influences occidentales. </t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="248.5" customHeight="1" s="20">
       <c r="A85" s="18" t="n">
@@ -4894,6 +5374,11 @@
           <t>philosophe et historien de la philosophie antique, dernier grand représentant de la philosophie religieuse de l'Âge d'argent russe.</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="311.15" customHeight="1" s="20">
       <c r="A86" s="18" t="n">
@@ -4947,6 +5432,14 @@
           <t xml:space="preserve">philosophe et historien russe qui  s’intéressa à l'esthétique  et a été un précurseur de la sociolinguistique. </t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O86">
+        <v>3</v>
+      </c>
     </row>
     <row r="87" ht="272.35" customHeight="1" s="20">
       <c r="A87" s="18" t="n">
@@ -5005,6 +5498,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="285.05" customHeight="1" s="20">
       <c r="A88" s="18" t="n">
@@ -5063,6 +5561,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="326.85" customHeight="1" s="20">
       <c r="A89" s="18" t="n">
@@ -5116,6 +5619,16 @@
           <t>philosophe russe naturalisé français, auteur d'une lecture de Hegel qui devint l'une des plus influentes du XXe siècle.</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="247.75" customHeight="1" s="20">
       <c r="A90" s="18" t="n">
@@ -5169,6 +5682,14 @@
           <t>philosophe russe  représentant de la théologie orthodoxe orientale.</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O90">
+        <v>2</v>
+      </c>
     </row>
     <row r="91" ht="94.75" customHeight="1" s="20">
       <c r="A91" s="18" t="n">
@@ -5222,6 +5743,11 @@
           <t xml:space="preserve">juive</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="213.4" customHeight="1" s="20">
       <c r="A92" s="18" t="n">
@@ -5270,6 +5796,11 @@
           <t>philosophe et logicien russe représentant  de la logique formelle et de la philosophie de la logique.</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="202.95" customHeight="1" s="20">
       <c r="A93" s="18" t="n">
@@ -5323,6 +5854,11 @@
           <t>philosophe  russe fondateur de l’école philosophique ‘dialogue des cultures’.</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="85.8" customHeight="1" s="20">
       <c r="A94" s="18" t="n">
@@ -5376,6 +5912,11 @@
           <t>théologien, prêtre orthodoxe et liturgiste russe-américain qui proposa un renouveau de la théologie liturgique.</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="284.3" customHeight="1" s="20">
       <c r="A95" s="18" t="n">
@@ -5429,6 +5970,11 @@
           <t>philosophe et sociologue russe qui donna  une satire impitoyable du système soviétique.</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="267.9" customHeight="1" s="20">
       <c r="A96" s="18" t="n">
@@ -5481,6 +6027,11 @@
       <c r="L96" s="19" t="inlineStr">
         <is>
           <t>philosophe marxiste russe qui entreprit de réhabiliter la dialectique hégélienne de la pensée.</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -2351,9 +2351,7 @@
           <t xml:space="preserve">russe</t>
         </is>
       </c>
-      <c r="O32">
-        <v>3</v>
-      </c>
+      <c r="O32"/>
     </row>
     <row r="33" ht="305.2" customHeight="1" s="20">
       <c r="A33" s="18" t="n">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -2632,7 +2632,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t xml:space="preserve">inde</t>
+          <t xml:space="preserve">inde;femme</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;femme</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -4147,6 +4147,11 @@
           <t>https://www.laphilo.fr/pho/nlossky-mini.webp</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/photo/nlossky.webp</t>
+        </is>
+      </c>
       <c r="J64" s="19" t="inlineStr">
         <is>
           <t>metaphysique ; spiritualite</t>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:P96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -653,6 +653,11 @@
           <t xml:space="preserve">Importance</t>
         </is>
       </c>
+      <c r="P3" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nationalité</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="186.75" customHeight="1" s="20">
       <c r="A4" s="18" t="n">
@@ -769,6 +774,11 @@
       <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ukrainienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Sophiologie</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="K65" s="19" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Sophiologie</t>
         </is>
       </c>
       <c r="L65" s="19" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="K74" s="19" t="inlineStr">
         <is>
-          <t>Spiritualisme ; Mysticisme</t>
+          <t xml:space="preserve">Spiritualisme ; Mysticisme ; Sophiologie</t>
         </is>
       </c>
       <c r="L74" s="19" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Eurasisme</t>
         </is>
       </c>
       <c r="L84" s="28" t="inlineStr">
@@ -6049,8 +6049,61 @@
       </c>
     </row>
     <row r="97" ht="163.5" customHeight="1" s="20">
-      <c r="E97" s="18" t="n"/>
+      <c r="A97" s="18">
+        <v>1890</v>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1938</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1890 – 1938</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikolaï TROUBETSKOÏ</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Sergue%C3%AFevitch_Troubetsko%C3%AF" title=" Wikipedia"&gt;Nikolaï TROUBETSKOÏ&lt;/a&gt; (Nikolaï Sergueïevitch Troubetskoï) est un linguiste et penseur russe, l’un des fondateurs de la phonologie moderne et le principal théoricien de l’&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;eurasisme&lt;/a&gt;. Né à Moscou en 1890 dans une grande famille princière, fils du philosophe Sergueï Troubetskoï, il publie à quinze ans ses premiers articles sur le folklore finno-ougrien et étudie la linguistique comparée à l’université de Moscou. Après la révolution, il quitte la Russie par la Crimée en 1920, enseigne à Sofia, puis à l’université de Vienne à partir de 1922.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;L’Europe et l’humanité&lt;/em&gt; (1920), il dénonce le « chauvinisme romano-germanique » qui fait passer la culture européenne pour la civilisation universelle et pousse les autres peuples à l’imiter au prix de leur identité. Avec le recueil &lt;em&gt;L’Exode vers l’Orient&lt;/em&gt; (1921), il fonde l’eurasisme : la Russie forme avec les peuples de la steppe une civilisation propre, l’Eurasie, dont il situe l’origine, dans &lt;em&gt;L’Héritage de Gengis Khan&lt;/em&gt; (1925), dans l’empire mongol. Ces idées rejoignent sa linguistique : des langues voisines, même sans parenté, finissent par se ressembler et forment des « &lt;a href="https://fr.wikipedia.org/wiki/Aire_linguistique" title=" Wikipedia"&gt;unions de langues&lt;/a&gt; ».&lt;/p&gt; &lt;p&gt;Au sein du &lt;a href="https://fr.wikipedia.org/wiki/Cercle_linguistique_de_Prague" title=" Wikipedia"&gt;Cercle linguistique de Prague&lt;/a&gt;, avec Roman Jakobson, il fonde la phonologie, qui étudie non les sons eux-mêmes mais leur fonction dans une langue : le phonème se définit par les oppositions qui distinguent les mots, comme « pain » et « bain ». Ses &lt;em&gt;Principes de phonologie&lt;/em&gt;, publiés après sa mort, sont un texte fondateur du structuralisme, qui inspirera Lévi-Strauss. Après l’annexion de l’Autriche, la Gestapo perquisitionne son appartement et confisque ses manuscrits ; il meurt peu après d’une crise cardiaque, en 1938.&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="G97" s="18" t="n"/>
+      <c r="H97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ntroubetskoi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; politique</t>
+        </is>
+      </c>
+      <c r="K97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eurasisme ; Structuralisme</t>
+        </is>
+      </c>
+      <c r="L97" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguiste russe, fondateur de la phonologie avec Jakobson et principal théoricien de l’eurasisme.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O97"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
     </row>
     <row r="1048563" ht="12.75" customHeight="1" s="20"/>
     <row r="1048564" ht="12.75" customHeight="1" s="20"/>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G20" s="19" t="inlineStr">
         <is>
-          <t>Bakounine pourquoi dieu empêche la révolution par le precepteur</t>
+          <t xml:space="preserve">Bakounine pourquoi dieu empêche la révolution par Le Précepteur</t>
         </is>
       </c>
       <c r="H20" s="19" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="G30" s="19" t="inlineStr">
         <is>
-          <t>N Strakhov par viktor lega</t>
+          <t xml:space="preserve">N Strakhov par Viktor Lega</t>
         </is>
       </c>
       <c r="H30" s="19" t="inlineStr">
@@ -2902,7 +2902,7 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>Kropotkine par Le precepteur</t>
+          <t xml:space="preserve">Kropotkine par Le Précepteur</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>Nikolai Kareev par see hear say learn</t>
+          <t xml:space="preserve">Nikolai Kareev par See Hear Say Learn</t>
         </is>
       </c>
       <c r="H48" s="19" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G52" s="19" t="inlineStr">
         <is>
-          <t>leo lopatin par see hear say learn</t>
+          <t xml:space="preserve">leo lopatin par See Hear Say Learn</t>
         </is>
       </c>
       <c r="H52" s="19" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="G59" s="19" t="inlineStr">
         <is>
-          <t>E. trubetskoy par viktor Lega</t>
+          <t xml:space="preserve">E. trubetskoy par Viktor Lega</t>
         </is>
       </c>
       <c r="H59" s="19" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="G61" s="19" t="inlineStr">
         <is>
-          <t>vycheslay Ivanov par see hear say learn</t>
+          <t xml:space="preserve">vycheslay Ivanov par See Hear Say Learn</t>
         </is>
       </c>
       <c r="H61" s="19" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="G69" s="19" t="inlineStr">
         <is>
-          <t>semyon frank par see hear say learn</t>
+          <t xml:space="preserve">semyon frank par See Hear Say Learn</t>
         </is>
       </c>
       <c r="H69" s="19" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Sophiologie</t>
+          <t xml:space="preserve">Spiritualisme ; Sophiologie ; Oecuménisme</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
@@ -3713,6 +3713,11 @@
           <t>Cosmisme</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">physicien et philosophe russe, père de l'astronautique et figure du cosmisme.</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">russe</t>
@@ -4230,7 +4235,7 @@
       </c>
       <c r="K65" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Sophiologie</t>
+          <t xml:space="preserve">Spiritualisme ; Sophiologie ; Oecuménisme</t>
         </is>
       </c>
       <c r="L65" s="19" t="inlineStr">
@@ -5321,7 +5326,7 @@
       </c>
       <c r="K84" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Eurasisme</t>
+          <t xml:space="preserve">Spiritualisme ; Eurasisme ; Oecuménisme</t>
         </is>
       </c>
       <c r="L84" s="28" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -801,7 +801,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mikha%C3%AFl_Chtcherbatov"  title=" Wikipedia"&gt;Mikhaïl CHTCHERBATOV&lt;/a&gt; était un historien, philosophe et homme d'État russe, figure majeure des Lumières russes . Prince de haute noblesse, il fut sénateur, membre du Collège du commerce et directeur de la Commission pour la rédaction du nouveau code de lois convoquée par Catherine II en 1767. Sa pensée combine l'admiration des Lumières occidentales — il connaissait bien Montesquieu, Locke et les philosophes français — avec un attachement profond aux prérogatives de l'aristocratie russe traditionnelle.&lt;/p&gt;&lt;p&gt;Son œuvre philosophique et historique majeure, l'&lt;em&gt;Histoire de Russie depuis les temps les plus anciens&lt;/em&gt; (7 volumes, 1770-1791), constitue la première grande synthèse historique de la Russie moderne, fondée sur un dépouillement minutieux des archives. Sa méthode, nourrie de l'érudition des Lumières, tranche avec les chroniques médiévales et représente un tournant dans l'historiographie russe. Dans son traité politique &lt;em&gt;De la corruption des mœurs en Russie&lt;/em&gt; (rédigé vers 1786-1787, publié seulement en 1858), il dresse &lt;a href="https://data.bris.ac.uk/datasets/3nmuogz0xzmpx21l2u1m5f3bjp/Mikhail%20Shcherbatov%20introduction.pdf"  title="Shcherbatov’s lettrers par data,bris"&gt; un tableau sévère &lt;/a&gt; de la décadence morale de la noblesse russe sous l'effet des réformes de Pierre le Grand et des emprunts culturels à l'Occident.&lt;/p&gt;&lt;p&gt;Ce texte, d'une franchise remarquable pour l'époque, critique aussi bien les monarques que l'aristocratie corrompue et témoigne d'un conservatisme éclairé original, distinct du simple réformisme des Lumières. Son &lt;em&gt;Voyage au pays d'Ophir&lt;/em&gt; (1783), une utopie politique, imagine un État idéal fondé sur les vertus nobiliaires et les principes philosophiques. Chtcherbatov représente la tension irrésolue, caractéristique de la pensée russe du XVIIIe siècle, entre l'aspiration aux Lumières et la défense des structures sociales traditionnelles.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Mikha%C3%AFl_Chtcherbatov"  title=" Wikipedia"&gt;Mikhaïl CHTCHERBATOV&lt;/a&gt; était un historien, philosophe et homme d'État russe, figure majeure des Lumières russes. Prince de haute noblesse, il fut sénateur, membre du Collège du commerce et directeur de la Commission pour la rédaction du nouveau code de lois convoquée par Catherine II en 1767. Sa pensée combine l'admiration des Lumières occidentales — il connaissait bien Montesquieu, Locke et les philosophes français — avec un attachement profond aux prérogatives de l'aristocratie russe traditionnelle.&lt;/p&gt;&lt;p&gt;Son œuvre philosophique et historique majeure, l'&lt;em&gt;Histoire de Russie depuis les temps les plus anciens&lt;/em&gt; (7 volumes, 1770-1791), constitue la première grande synthèse historique de la Russie moderne, fondée sur un dépouillement minutieux des archives. Sa méthode, nourrie de l'érudition des Lumières, tranche avec les chroniques médiévales et représente un tournant dans l'historiographie russe. Dans son traité politique &lt;em&gt;De la corruption des mœurs en Russie&lt;/em&gt; (rédigé vers 1786-1787, publié seulement en 1858), il dresse &lt;a href="https://data.bris.ac.uk/datasets/3nmuogz0xzmpx21l2u1m5f3bjp/Mikhail%20Shcherbatov%20introduction.pdf"  title="Shcherbatov’s lettrers par data,bris"&gt; un tableau sévère &lt;/a&gt; de la décadence morale de la noblesse russe sous l'effet des réformes de Pierre le Grand et des emprunts culturels à l'Occident.&lt;/p&gt;&lt;p&gt;Ce texte, d'une franchise remarquable pour l'époque, critique aussi bien les monarques que l'aristocratie corrompue et témoigne d'un conservatisme éclairé original, distinct du simple réformisme des Lumières. Son &lt;em&gt;Voyage au pays d'Ophir&lt;/em&gt; (1783), une utopie politique, imagine un État idéal fondé sur les vertus nobiliaires et les principes philosophiques. Chtcherbatov représente la tension irrésolue, caractéristique de la pensée russe du XVIIIe siècle, entre l'aspiration aux Lumières et la défense des structures sociales traditionnelles.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F6" s="18" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E30" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Strakhov" title=" Wikipedia"&gt;Nikolaï STRAKHOV&lt;/a&gt; était un philosophe, critique littéraire et naturaliste russe, l'une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Potchvennitchestvo"  title="potchvennitchestvo par wikipedia"&gt;Potchvennitchestvo &lt;/a&gt; , mouvement philosophique et culturel qui cherchait à enraciner la pensée russe dans les valeurs organiques du peuple. Ami intime de Dostoïevski et collaborateur des revues slavophiles, il fut l'un des principaux médiateurs de la philosophie occidentale pour le public russe éduqué, notamment de la pensée de Hegel, Schopenhauer et Nietzsche.&lt;/p&gt;&lt;p&gt;Sa philosophie s'articule autour d'une critique du positivisme et du matérialisme dominants dans les sciences naturelles de son temps. Dans ses &lt;em&gt;Lettres sur la philosophie organique&lt;/em&gt; et ses essais philosophiques, il défend une conception de la nature comme organisme vivant hiérarchiquement organisé, contre le mécanisme réductionniste. Sa philosophie de la biologie, influencée par Cuvier  postule que les lois organiques sont irréductibles aux lois physico-chimiques et que la vie est le principe explicatif fondamental du cosmos plutôt qu'un épiphénomène de la matière.&lt;/p&gt;&lt;p&gt;Ses travaux de critique littéraire, notamment ses études sur Tolstoï et Dostoïevski, sont des analyses philosophiques de grande valeur qui replacent l'œuvre littéraire dans le contexte de la pensée nationale russe. Sa polémique avec les penseurs positivistes et nihilistes de sa génération (Tchernychevski, Pissarev) illustre la tension fondamentale de la vie intellectuelle russe des années 1860-1880 entre matérialisme révolutionnaire et idéalisme conservateur. Il représente un conservatisme philosophique cultivé et nuancé, éloigné des simplifications nationalistes mais profondément attaché à la spécificité de la culture russe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Strakhov" title=" Wikipedia"&gt;Nikolaï STRAKHOV&lt;/a&gt; était un philosophe, critique littéraire et naturaliste russe, l'une des figures les plus représentatives du &lt;a href="https://fr.wikipedia.org/wiki/Potchvennitchestvo"  title="potchvennitchestvo par wikipedia"&gt;Potchvennitchestvo&lt;/a&gt;, mouvement philosophique et culturel qui cherchait à enraciner la pensée russe dans les valeurs organiques du peuple. Ami intime de Dostoïevski et collaborateur des revues slavophiles, il fut l'un des principaux médiateurs de la philosophie occidentale pour le public russe éduqué, notamment de la pensée de Hegel, Schopenhauer et Nietzsche.&lt;/p&gt;&lt;p&gt;Sa philosophie s'articule autour d'une critique du positivisme et du matérialisme dominants dans les sciences naturelles de son temps. Dans ses &lt;em&gt;Lettres sur la philosophie organique&lt;/em&gt; et ses essais philosophiques, il défend une conception de la nature comme organisme vivant hiérarchiquement organisé, contre le mécanisme réductionniste. Sa philosophie de la biologie, influencée par Cuvier  postule que les lois organiques sont irréductibles aux lois physico-chimiques et que la vie est le principe explicatif fondamental du cosmos plutôt qu'un épiphénomène de la matière.&lt;/p&gt;&lt;p&gt;Ses travaux de critique littéraire, notamment ses études sur Tolstoï et Dostoïevski, sont des analyses philosophiques de grande valeur qui replacent l'œuvre littéraire dans le contexte de la pensée nationale russe. Sa polémique avec les penseurs positivistes et nihilistes de sa génération (Tchernychevski, Pissarev) illustre la tension fondamentale de la vie intellectuelle russe des années 1860-1880 entre matérialisme révolutionnaire et idéalisme conservateur. Il représente un conservatisme philosophique cultivé et nuancé, éloigné des simplifications nationalistes mais profondément attaché à la spécificité de la culture russe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nikolai_Fyodorov_(philosopher)"   title=" Wikipedia"&gt;Nikolaï FEDOROV&lt;/a&gt; était un philosophe russe excentrique et visionnaire, fondateur du courant de pensée appelé « cosmisme russe ». Fils illégitime d'un noble, il vécut dans une austérité ascétique totale, travaillant comme bibliothécaire au musée Roumiantsev de Moscou, donnant la quasi-totalité de ses maigres revenus aux pauvres et ne publiant rien de son vivant. Sa pensée, transmise par ses manuscrits et ses conversations, fascina Tolstoï, Dostoïevski et Soloviev. &lt;/p&gt; &lt;p&gt; Sa philosophie, exposée dans &lt;em&gt;La Philosophie de l'œuvre commune&lt;/em&gt; (publiée posthumement en 1906), est une utopie technologique et spirituelle d'une ambition sans précédent. Son idée centrale est la « tâche commune » de l'humanité :  &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_47_1_1196"  title="fiodorov le salut de l’humanité  par persée"&gt;la résurrection littérale &lt;/a&gt; de tous les morts. il soutient que si Dieu a promis la résurrection, les hommes ont le devoir d'y contribuer activement par la science, la technique et la solidarité universelle. Ce projet implique la maîtrise totale des forces naturelles, la régulation du cosmos et la transformation de l'humanité en une fraternité universelle transcendant la mort. &lt;/p&gt; &lt;p&gt; Cette pensée, qui peut sembler délirante, est en réalité un système cohérent articulant métaphysique chrétienne, éthique de la solidarité et foi dans la puissance de la raison et de la technique.&lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_46_1_1166"  title="le cosmisme russe  par persée"&gt; Le cosmisme russe &lt;/a&gt;  qu'il inaugure influença profondément les pionniers de l'astronautique russe (Tsiolkovsky, qui fut son lecteur), le mouvement transhumaniste contemporain et de nombreux artistes et penseurs russes du XXe siècle. Il est aujourd'hui reconnu comme l'un des précurseurs les plus originaux des débats contemporains sur la mort, la technique et l'immortalité. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nikolai_Fyodorov_(philosopher)"   title=" Wikipedia"&gt;Nikolaï FEDOROV&lt;/a&gt; était un philosophe russe excentrique et visionnaire, fondateur du courant de pensée appelé « cosmisme russe ». Fils illégitime d'un noble, il vécut dans une austérité ascétique totale, travaillant comme bibliothécaire au musée Roumiantsev de Moscou, donnant la quasi-totalité de ses maigres revenus aux pauvres et ne publiant rien de son vivant. Sa pensée, transmise par ses manuscrits et ses conversations, fascina Tolstoï, Dostoïevski et Soloviev. &lt;/p&gt; &lt;p&gt; Sa philosophie, exposée dans &lt;em&gt;La Philosophie de l'œuvre commune&lt;/em&gt; (publiée posthumement en 1906), est une utopie technologique et spirituelle d'une ambition sans précédent. Son idée centrale est la « tâche commune » de l'humanité :  &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_47_1_1196"  title="fiodorov le salut de l’humanité  par persée"&gt;la résurrection littérale &lt;/a&gt; de tous les morts. Il soutient que si Dieu a promis la résurrection, les hommes ont le devoir d'y contribuer activement par la science, la technique et la solidarité universelle. Ce projet implique la maîtrise totale des forces naturelles, la régulation du cosmos et la transformation de l'humanité en une fraternité universelle transcendant la mort. &lt;/p&gt; &lt;p&gt; Cette pensée, qui peut sembler délirante, est en réalité un système cohérent articulant métaphysique chrétienne, éthique de la solidarité et foi dans la puissance de la raison et de la technique.&lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_46_1_1166"  title="le cosmisme russe  par persée"&gt; Le cosmisme russe &lt;/a&gt;  qu'il inaugure influença profondément les pionniers de l'astronautique russe (Tsiolkovsky, qui fut son lecteur), le mouvement transhumaniste contemporain et de nombreux artistes et penseurs russes du XXe siècle. Il est aujourd'hui reconnu comme l'un des précurseurs les plus originaux des débats contemporains sur la mort, la technique et l'immortalité. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E35" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ivan_Sechenov" title=" Wikipedia"&gt;Ivan SETCHENOV&lt;/a&gt; était un physiologiste et philosophe matérialiste russe, fondateur de la physiologie scientifique en Russie et figure importante du courant matérialiste et nihiliste des années 1860. Son œuvre majeure, &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; (1863), constitue un texte fondateur de la neurophysiologie moderne et un manifeste philosophique .&lt;a href="https://fr.topwar.ru/86439-otec-russkoy-fiziologii-ivan-mihaylovich-sechenov.html"  title="pere de la physiologie russe par top war"&gt; du matérialisme scientifique &lt;/a&gt; en Russie.&lt;/p&gt;&lt;p&gt;Sa thèse centrale dans &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; — publiée d'abord dans la revue radicale &lt;em&gt;Sovremennik&lt;/em&gt; avant d'être censurée par les autorités — est que toutes les activités de l'esprit, y compris les plus complexes (pensée, volonté, sentiments), sont des réflexes cérébraux de différents degrés de complexité. Cette thèse, qui réduisait la vie psychique à des processus nerveux matériels, fut accueillie avec enthousiasme par les nihilistes et les radicaux (qui y voyaient la confirmation scientifique de leur matérialisme), et avec consternation par les conservateurs et les théologiens. Elle déclencha un intense débat philosophique sur le rapport entre le corps et l'esprit, entre science et morale.&lt;/p&gt;&lt;p&gt;Sa physiologie du cerveau et des sens, développée dans des travaux expérimentaux rigoureux tout au long de sa carrière, contribua de manière fondamentale au développement des neurosciences. Son influence sur Pavlov — qui cite explicitement &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; comme source de sa théorie du réflexe conditionné — fut déterminante pour le développement de la physiologie russe et mondiale au XXe siècle. Il incarne le type du savant-philosophe du XIXe siècle, pour qui la découverte scientifique a des implications philosophiques directes et révolutionnaires.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ivan_Sechenov" title=" Wikipedia"&gt;Ivan SETCHENOV&lt;/a&gt; était un physiologiste et philosophe matérialiste russe, fondateur de la physiologie scientifique en Russie et figure importante du courant matérialiste et nihiliste des années 1860. Son œuvre majeure, &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; (1863), constitue un texte fondateur de la neurophysiologie moderne et un manifeste philosophique &lt;a href="https://fr.topwar.ru/86439-otec-russkoy-fiziologii-ivan-mihaylovich-sechenov.html"  title="pere de la physiologie russe par top war"&gt; du matérialisme scientifique &lt;/a&gt; en Russie.&lt;/p&gt;&lt;p&gt;Sa thèse centrale dans &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; — publiée d'abord dans la revue radicale &lt;em&gt;Sovremennik&lt;/em&gt; avant d'être censurée par les autorités — est que toutes les activités de l'esprit, y compris les plus complexes (pensée, volonté, sentiments), sont des réflexes cérébraux de différents degrés de complexité. Cette thèse, qui réduisait la vie psychique à des processus nerveux matériels, fut accueillie avec enthousiasme par les nihilistes et les radicaux (qui y voyaient la confirmation scientifique de leur matérialisme), et avec consternation par les conservateurs et les théologiens. Elle déclencha un intense débat philosophique sur le rapport entre le corps et l'esprit, entre science et morale.&lt;/p&gt;&lt;p&gt;Sa physiologie du cerveau et des sens, développée dans des travaux expérimentaux rigoureux tout au long de sa carrière, contribua de manière fondamentale au développement des neurosciences. Son influence sur Pavlov — qui cite explicitement &lt;em&gt;Les Réflexes du cerveau&lt;/em&gt; comme source de sa théorie du réflexe conditionné — fut déterminante pour le développement de la physiologie russe et mondiale au XXe siècle. Il incarne le type du savant-philosophe du XIXe siècle, pour qui la découverte scientifique a des implications philosophiques directes et révolutionnaires.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H35" s="19" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky"  title=" Wikipedia"&gt;Helena BLAVATSKY&lt;/a&gt; était une ésotériste, philosophe et écrivaine russe, cofondatrice de  &lt;a href="https://www.retronews.fr/religions/echo-de-presse/2019/01/08/la-societe-theosophique"  title=" société théosophique par retronews"&gt;la Société Théosophique &lt;/a&gt;  (1875) et l'une des figures les plus influentes du renouveau spirituel occidental du XIXe siècle. Née à Ekaterinoslav dans une famille de la haute noblesse russe, elle mena une vie d'aventures extraordinaires — voyages en Orient, séjours en Inde, en Tibet et en Égypte, contacts avec des traditions initiatiques variées — avant de s'établir en Occident et de codifier sa synthèse philosophique universelle qu'elle appela la Théosophie.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans ses deux œuvres maîtresses, &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), constitue une tentative ambitieuse de synthèse universelle des traditions ésotériques de l'humanité — hermétisme occidental, néoplatonisme, kabbale, vedanta hindou, bouddhisme tibétain — au service d'une vision du cosmos comme processus évolutif spirituel. Sa doctrine postule l'existence d'une sagesse primordiale commune à toutes les religions, transmise par une fraternité de Maîtres spirituels, et une vision de &lt;a href="https://www.youtube.com/watch?v=9DfSgzjyliQ"  title="l’évolution de l’homme par nouvelle acropole france "&gt;l'évolution de l'homme &lt;/a&gt; comme processus de retour de l'esprit vers sa source divine.&lt;/p&gt;&lt;p&gt;Bien que contestée par certains milieux scientifiques et religieux de son temps, son influence sur la culture occidentale fut considérable : elle contribua à &lt;a href="https://www.youtube.com/watch?v=icg5koa5YGE"  title="l’autosabotage de l’ame par enseignement de Blavatsky "&gt;l'orientalisation de la spiritualité occidentale &lt;/a&gt; , inspira des figures aussi diverses que W.B. Yeats, Kandinsky, Mondrian et Gandhi, et préfigura nombre de thèmes du Nouvel Âge contemporain. En Russie, son influence alimenta le symbolisme et le mysticisme du tournant du XXe siècle. Elle reste une figure controversée mais incontournable de l'histoire des idées ésotériques modernes.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Helena_Blavatsky"  title=" Wikipedia"&gt;Helena BLAVATSKY&lt;/a&gt; était une ésotériste, philosophe et écrivaine russe, cofondatrice de  &lt;a href="https://www.retronews.fr/religions/echo-de-presse/2019/01/08/la-societe-theosophique"  title=" société théosophique par retronews"&gt;la Société Théosophique &lt;/a&gt;  (1875) et l'une des figures les plus influentes du renouveau spirituel occidental du XIXe siècle. Née à Ekaterinoslav dans une famille de la haute noblesse russe, elle mena une vie d'aventures extraordinaires — voyages en Orient, séjours en Inde, en Tibet et en Égypte, contacts avec des traditions initiatiques variées — avant de s'établir en Occident et de codifier sa synthèse philosophique universelle qu'elle appela la Théosophie.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans ses deux œuvres maîtresses, &lt;em&gt;Isis dévoilée&lt;/em&gt; (1877) et &lt;em&gt;La Doctrine secrète&lt;/em&gt; (1888), constitue une tentative ambitieuse de synthèse universelle des traditions ésotériques de l'humanité — hermétisme occidental, néoplatonisme, kabbale, vedanta hindou, bouddhisme tibétain — au service d'une vision du cosmos comme processus évolutif spirituel. Sa doctrine postule l'existence d'une sagesse primordiale commune à toutes les religions, transmise par une fraternité de Maîtres spirituels, et une vision de &lt;a href="https://www.youtube.com/watch?v=9DfSgzjyliQ"  title="l’évolution de l’homme par nouvelle acropole france "&gt;l'évolution de l'homme &lt;/a&gt; comme processus de retour de l'esprit vers sa source divine.&lt;/p&gt;&lt;p&gt;Bien que contestée par certains milieux scientifiques et religieux de son temps, son influence sur la culture occidentale fut considérable : elle contribua à &lt;a href="https://www.youtube.com/watch?v=icg5koa5YGE"  title="l’autosabotage de l’ame par enseignement de Blavatsky "&gt;l'orientalisation de la spiritualité occidentale&lt;/a&gt;, inspira des figures aussi diverses que W.B. Yeats, Kandinsky, Mondrian et Gandhi, et préfigura nombre de thèmes du Nouvel Âge contemporain. En Russie, son influence alimenta le symbolisme et le mysticisme du tournant du XXe siècle. Elle reste une figure controversée mais incontournable de l'histoire des idées ésotériques modernes.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev_(philosophe)https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion &lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev_(philosophe)https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion&lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E53" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Innokenti_Annenski" title=" Wikipedia"&gt;Innokenti ANNENSKI&lt;/a&gt; était un poète, critique littéraire et helléniste russe, l'une des figures les plus importantes du symbolisme russe et un précurseur du courant acméiste. Directeur de gymnase à Tsarskoïe Selo et fin connaisseur de la culture grecque antique qu'il traduisit abondamment, il développa une poésie d'une densité et d'une profondeur exceptionnelles, longtemps méconnue de ses contemporains mais reconnue après sa mort comme l'une des grandes œuvres de la poésie russe du tournant du XXe siècle.&lt;/p&gt;&lt;p&gt;Sa   &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2012_num_34_1_2473" titre="annenski par persée "&gt;philosophie poétique et esthétique &lt;/a&gt; , exposée dans ses deux recueils de critiques &lt;em&gt;Le Livre des reflets&lt;/em&gt; (1906 et 1909), s'organise autour d'une méditation sur la souffrance, l'anxiété et l'impossibilité d'échapper à la conscience de soi. Sa poésie explore avec une précision quasi phénoménologique les états d'âme les plus fugaces et les plus douloureux — l'ennui, l'angoisse, la nostalgie, la présence du temps qui s'écoule. Influencé par les symbolistes français (Verlaine, Mallarmé) qu'il connaissait bien, il leur apporta une profondeur existentielle et une sensibilité au quotidien qui lui sont propres.&lt;/p&gt;&lt;p&gt;Ses traductions de toute la tragédie grecque (Euripide notamment) et ses études hellénistiques témoignent d'une culture classique exceptionnelle mise au service d'une sensibilité résolument moderne. Sa poésie et sa critique influencèrent profondément Akhmatova, Mandelstam et  &lt;a href="https://fr.wikipedia.org/wiki/Acm%C3%A9isme" titre="acméisme par wikipedia "&gt;les acméistes &lt;/a&gt; qui le reconnurent comme l'un de leurs précurseurs spirituels. Mort d'une attaque cardiaque en 1909, il laissa une œuvre qui ne fut pleinement reconnue et éditée que plusieurs décennies après sa mort, illustrant le paradoxe du génie méconnu de son vivant.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Innokenti_Annenski" title=" Wikipedia"&gt;Innokenti ANNENSKI&lt;/a&gt; était un poète, critique littéraire et helléniste russe, l'une des figures les plus importantes du symbolisme russe et un précurseur du courant acméiste. Directeur de gymnase à Tsarskoïe Selo et fin connaisseur de la culture grecque antique qu'il traduisit abondamment, il développa une poésie d'une densité et d'une profondeur exceptionnelles, longtemps méconnue de ses contemporains mais reconnue après sa mort comme l'une des grandes œuvres de la poésie russe du tournant du XXe siècle.&lt;/p&gt;&lt;p&gt;Sa   &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2012_num_34_1_2473" titre="annenski par persée "&gt;philosophie poétique et esthétique&lt;/a&gt;, exposée dans ses deux recueils de critiques &lt;em&gt;Le Livre des reflets&lt;/em&gt; (1906 et 1909), s'organise autour d'une méditation sur la souffrance, l'anxiété et l'impossibilité d'échapper à la conscience de soi. Sa poésie explore avec une précision quasi phénoménologique les états d'âme les plus fugaces et les plus douloureux — l'ennui, l'angoisse, la nostalgie, la présence du temps qui s'écoule. Influencé par les symbolistes français (Verlaine, Mallarmé) qu'il connaissait bien, il leur apporta une profondeur existentielle et une sensibilité au quotidien qui lui sont propres.&lt;/p&gt;&lt;p&gt;Ses traductions de toute la tragédie grecque (Euripide notamment) et ses études hellénistiques témoignent d'une culture classique exceptionnelle mise au service d'une sensibilité résolument moderne. Sa poésie et sa critique influencèrent profondément Akhmatova, Mandelstam et  &lt;a href="https://fr.wikipedia.org/wiki/Acm%C3%A9isme" titre="acméisme par wikipedia "&gt;les acméistes &lt;/a&gt; qui le reconnurent comme l'un de leurs précurseurs spirituels. Mort d'une attaque cardiaque en 1909, il laissa une œuvre qui ne fut pleinement reconnue et éditée que plusieurs décennies après sa mort, illustrant le paradoxe du génie méconnu de son vivant.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H53" s="19" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="E64" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Lossky" title=" Wikipedia"&gt;Nicolas LOSSKY&lt;/a&gt; était un philosophe russe, fondateur du courant de  &lt;a href="https://dioceseparis.fr/le-pere-serge-boulgakov-et-le.html" titre="mouvement oecuménique par dioceseparis"&gt;l'intuitivisme en philosophie &lt;/a&gt;  russe et l'un des représentants les plus importants du personnalisme chrétien. Professeur à l'Université de Saint-Pétersbourg, il fut expulsé de Russie soviétique en 1922 sur le « bateau des philosophes » et s'établit successivement à Prague, Paris et finalement aux États-Unis, où il enseigna jusqu'à sa mort. Son œuvre constitue l'une des synthèses les plus rigoureuses et les plus complètes de la philosophie personnaliste et métaphysique russe du XXe siècle.&lt;/p&gt;&lt;p&gt;Sa philosophie est fondée sur la théorie de l'intuitivisme : la conscience humaine saisit directement la réalité transcendante, non par des représentations ou des idées intermédiaires, mais par une appréhension intuitive immédiate. Dans son œuvre maîtresse, &lt;em&gt;La Connaissance intuitive comme fondement de la connaissance&lt;/em&gt; (1906), il développe une  &lt;a href="https://www.youtube.com/watch?v=5BlWpR4xXeg" titre="nicolay lossky par dee hear say learn"&gt;théorie de la connaissance &lt;/a&gt; qui reconnaît à l'intuition sensible, intellectuelle et mystique un accès direct à la réalité des objets. Cette position  le distingue à la fois du kantisme (qui interpose des formes a priori entre le sujet et la réalité) et du phénoménalisme empiriste.&lt;/p&gt;&lt;p&gt;Sa métaphysique personnaliste hiérarchique, exposée dans &lt;em&gt;Le Monde comme réalisation organique&lt;/em&gt; (1917) et dans son &lt;em&gt;Histoire de la philosophie russe&lt;/em&gt; , conçoit l'univers comme une communauté hiérarchique d'êtres personnels animés par l'amour et tendant vers la communion avec Dieu. Son &lt;em&gt;Histoire de la philosophie russe&lt;/em&gt; reste l'une des meilleures introductions à la pensée philosophique russe disponibles en langue occidentale. Il représente le meilleur de la tradition philosophique personnaliste et intuitiviste russe, synthétisant rigueur académique et profondeur spirituelle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_Lossky" title=" Wikipedia"&gt;Nicolas LOSSKY&lt;/a&gt; était un philosophe russe, fondateur du courant de  &lt;a href="https://dioceseparis.fr/le-pere-serge-boulgakov-et-le.html" titre="mouvement oecuménique par dioceseparis"&gt;l'intuitivisme en philosophie &lt;/a&gt;  russe et l'un des représentants les plus importants du personnalisme chrétien. Professeur à l'Université de Saint-Pétersbourg, il fut expulsé de Russie soviétique en 1922 sur le « bateau des philosophes » et s'établit successivement à Prague, Paris et finalement aux États-Unis, où il enseigna jusqu'à sa mort. Son œuvre constitue l'une des synthèses les plus rigoureuses et les plus complètes de la philosophie personnaliste et métaphysique russe du XXe siècle.&lt;/p&gt;&lt;p&gt;Sa philosophie est fondée sur la théorie de l'intuitivisme : la conscience humaine saisit directement la réalité transcendante, non par des représentations ou des idées intermédiaires, mais par une appréhension intuitive immédiate. Dans son œuvre maîtresse, &lt;em&gt;La Connaissance intuitive comme fondement de la connaissance&lt;/em&gt; (1906), il développe une  &lt;a href="https://www.youtube.com/watch?v=5BlWpR4xXeg" titre="nicolay lossky par dee hear say learn"&gt;théorie de la connaissance &lt;/a&gt; qui reconnaît à l'intuition sensible, intellectuelle et mystique un accès direct à la réalité des objets. Cette position  le distingue à la fois du kantisme (qui interpose des formes a priori entre le sujet et la réalité) et du phénoménalisme empiriste.&lt;/p&gt;&lt;p&gt;Sa métaphysique personnaliste hiérarchique, exposée dans &lt;em&gt;Le Monde comme réalisation organique&lt;/em&gt; (1917) et dans son &lt;em&gt;Histoire de la philosophie russe&lt;/em&gt;, conçoit l'univers comme une communauté hiérarchique d'êtres personnels animés par l'amour et tendant vers la communion avec Dieu. Son &lt;em&gt;Histoire de la philosophie russe&lt;/em&gt; reste l'une des meilleures introductions à la pensée philosophique russe disponibles en langue occidentale. Il représente le meilleur de la tradition philosophique personnaliste et intuitiviste russe, synthétisant rigueur académique et profondeur spirituelle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="E67" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Val%C3%A9ri_Brioussov" title=" Wikipedia"&gt;Valéry BRIOUSSOV&lt;/a&gt; était un poète, écrivain et théoricien russe, l'un des fondateurs et des organisateurs les plus actifs du mouvement symboliste russe. Fondateur et animateur de la maison d'édition symboliste &lt;em&gt;Skorpion&lt;/em&gt; et de la revue &lt;em&gt;Vesy&lt;/em&gt; (La Balance), il fut le premier à donner une forme institutionnelle au  &lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_russe"  title="symbolisme russe par wikipedia"&gt;symbolisme russe, &lt;/a&gt; le dotant d'une revue, d'une maison d'édition et d'un programme esthétique cohérent.&lt;/p&gt;&lt;p&gt;Sa philosophie esthétique, exposée dans ses manifestes et ses articles critiques, s'inscrit dans la tradition du symbolisme décadent français tout en lui imprimant une marque personnelle. Pour lui, l'art est avant tout affaire de technique : le poète n'est pas un prophète ou un mystique mais un artisan de la langue, maître des formes et des rythmes. Cette conception formaliste du symbolisme le distingue de Biély ou d'Ivanov qui insistaient sur la dimension métaphysique et théurgique de l'art symboliste. Sa poésie, d'une beauté  &lt;a href="https://www.youtube.com/watch?v=55Y2mhEBps0"  title="the republic of the southern cross par weird and the wonderful"&gt;formelle rigoureuse, &lt;/a&gt; explore les thèmes de l'amour, de la mort, du destin et de la civilisation avec une maîtrise technique exceptionnelle.&lt;/p&gt;&lt;p&gt;Son attitude envers la révolution bolchevique fut ambiguë mais pragmatique : il rejoignit le Parti communiste en 1920 et collabora activement avec les institutions culturelles soviétiques, voyant dans la révolution une force comparable aux grandes transformations historiques du passé. Sa poésie tardive, moins bien reçue que ses œuvres de jeunesse, illustre les tensions entre l'idéal esthétique symboliste et les exigences de la culture révolutionnaire. il incarne la figure du poète-organisateur, dont le talent de gestionnaire culturel égale ou dépasse le talent créateur.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Val%C3%A9ri_Brioussov" title=" Wikipedia"&gt;Valéry BRIOUSSOV&lt;/a&gt; était un poète, écrivain et théoricien russe, l'un des fondateurs et des organisateurs les plus actifs du mouvement symboliste russe. Fondateur et animateur de la maison d'édition symboliste &lt;em&gt;Skorpion&lt;/em&gt; et de la revue &lt;em&gt;Vesy&lt;/em&gt; (La Balance), il fut le premier à donner une forme institutionnelle au  &lt;a href="https://fr.wikipedia.org/wiki/Symbolisme_russe"  title="symbolisme russe par wikipedia"&gt;symbolisme russe, &lt;/a&gt; le dotant d'une revue, d'une maison d'édition et d'un programme esthétique cohérent.&lt;/p&gt;&lt;p&gt;Sa philosophie esthétique, exposée dans ses manifestes et ses articles critiques, s'inscrit dans la tradition du symbolisme décadent français tout en lui imprimant une marque personnelle. Pour lui, l'art est avant tout affaire de technique : le poète n'est pas un prophète ou un mystique mais un artisan de la langue, maître des formes et des rythmes. Cette conception formaliste du symbolisme le distingue de Biély ou d'Ivanov qui insistaient sur la dimension métaphysique et théurgique de l'art symboliste. Sa poésie, d'une beauté  &lt;a href="https://www.youtube.com/watch?v=55Y2mhEBps0"  title="the republic of the southern cross par weird and the wonderful"&gt;formelle rigoureuse, &lt;/a&gt; explore les thèmes de l'amour, de la mort, du destin et de la civilisation avec une maîtrise technique exceptionnelle.&lt;/p&gt;&lt;p&gt;Son attitude envers la révolution bolchevique fut ambiguë mais pragmatique : il rejoignit le Parti communiste en 1920 et collabora activement avec les institutions culturelles soviétiques, voyant dans la révolution une force comparable aux grandes transformations historiques du passé. Sa poésie tardive, moins bien reçue que ses œuvres de jeunesse, illustre les tensions entre l'idéal esthétique symboliste et les exigences de la culture révolutionnaire. Il incarne la figure du poète-organisateur, dont le talent de gestionnaire culturel égale ou dépasse le talent créateur.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mikhail_Lifshitz" title=" Wikipedia"&gt;Mikhaïl LIFSHITZ&lt;/a&gt; était un philosophe, esthéticien et critique d'art marxiste soviétique, l'un des penseurs les plus indépendants et les plus courageux de la philosophie soviétique du XXe siècle. Collaborateur et ami de György Lukács dans les années 1930, il développa avec lui une esthétique marxiste fondée sur l'idéal du réalisme classique contre le formalisme moderniste. Ses travaux sur Marx et l'art, sur Hegel et l'esthétique, et sur la théorie de la connaissance constituent des contributions importantes au marxisme critique.&lt;/p&gt;&lt;p&gt; &lt;a href="https://www.goodreads.com/author/show/7111845.Mikhail_Lifshitz"  title="Lifshitz par goodreads"&gt;Sa philosophie esthétique &lt;/a&gt; s'oppose à la fois au formalisme abstrait (l'art pour l'art) et au réalisme socialiste bureaucratique. S'appuyant sur une lecture attentive des textes de Marx et d'Engels sur l'art, il développe une théorie de la mimesis — la représentation fidèle de la réalité dans sa richesse et ses contradictions — comme fondement de toute grande création artistique. Pour lui, les grands artistes (Homère, Shakespeare, Goethe, Tolstoï) ont su saisir la totalité vivante de leur époque à travers des images concrètes, et c'est cette richesse concrète qui fait la valeur éternelle de leur œuvre.&lt;/p&gt;&lt;p&gt;Son courage intellectuel se manifesta dans sa résistance aux dérives dogmatiques  &lt;a href="https://fr.wikipedia.org/wiki/Jdanovisme_artistique"  title="jdanovisme artistique par wikipedia"&gt;du jdanovisme &lt;/a&gt;, qu'il critiqua avec une ironie mordante sous couvert de fidélité au marxisme classique. Ses travaux sur Lénine et la dialectique, et sa polémique avec les courants structuralistes et sémiotiques des années 1960-1970, témoignent d'une pensée marxiste indépendante et rigoureuse. Il représente le meilleur de l'héritage critique du marxisme soviétique, en rupture avec ses simplifications dogmatiques.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mikhail_Lifshitz" title=" Wikipedia"&gt;Mikhaïl LIFSHITZ&lt;/a&gt; était un philosophe, esthéticien et critique d'art marxiste soviétique, l'un des penseurs les plus indépendants et les plus courageux de la philosophie soviétique du XXe siècle. Collaborateur et ami de György Lukács dans les années 1930, il développa avec lui une esthétique marxiste fondée sur l'idéal du réalisme classique contre le formalisme moderniste. Ses travaux sur Marx et l'art, sur Hegel et l'esthétique, et sur la théorie de la connaissance constituent des contributions importantes au marxisme critique.&lt;/p&gt;&lt;p&gt; &lt;a href="https://www.goodreads.com/author/show/7111845.Mikhail_Lifshitz"  title="Lifshitz par goodreads"&gt;Sa philosophie esthétique &lt;/a&gt; s'oppose à la fois au formalisme abstrait (l'art pour l'art) et au réalisme socialiste bureaucratique. S'appuyant sur une lecture attentive des textes de Marx et d'Engels sur l'art, il développe une théorie de la mimesis — la représentation fidèle de la réalité dans sa richesse et ses contradictions — comme fondement de toute grande création artistique. Pour lui, les grands artistes (Homère, Shakespeare, Goethe, Tolstoï) ont su saisir la totalité vivante de leur époque à travers des images concrètes, et c'est cette richesse concrète qui fait la valeur éternelle de leur œuvre.&lt;/p&gt;&lt;p&gt;Son courage intellectuel se manifesta dans sa résistance aux dérives dogmatiques  &lt;a href="https://fr.wikipedia.org/wiki/Jdanovisme_artistique"  title="jdanovisme artistique par wikipedia"&gt;du jdanovisme&lt;/a&gt;, qu'il critiqua avec une ironie mordante sous couvert de fidélité au marxisme classique. Ses travaux sur Lénine et la dialectique, et sa polémique avec les courants structuralistes et sémiotiques des années 1960-1970, témoignent d'une pensée marxiste indépendante et rigoureuse. Il représente le meilleur de l'héritage critique du marxisme soviétique, en rupture avec ses simplifications dogmatiques.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H91" s="19" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -3690,12 +3690,12 @@
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>2y2OwyOTxQM</t>
+          <t xml:space="preserve">TgUHH3oaajc</t>
         </is>
       </c>
       <c r="G56" s="19" t="inlineStr">
         <is>
-          <t>Tsiolkovski, instituteur sourd par etienne beaumont</t>
+          <t xml:space="preserve">"Konstantin Tsiolkovski : le visionnaire sourd pionnier de l'exploration spatiale" par astris</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -3938,7 +3938,7 @@
       </c>
       <c r="K60" s="19" t="inlineStr">
         <is>
-          <t>Existentialisme</t>
+          <t xml:space="preserve">Existentialisme ; Absurde</t>
         </is>
       </c>
       <c r="L60" s="19" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="K73" s="19" t="inlineStr">
         <is>
-          <t>Symbolisme</t>
+          <t xml:space="preserve">Symbolisme ; Anthroposophie</t>
         </is>
       </c>
       <c r="L73" s="19" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="K90" s="19" t="inlineStr">
         <is>
-          <t>Spiritualisme</t>
+          <t xml:space="preserve">Spiritualisme ; Hésychasme</t>
         </is>
       </c>
       <c r="L90" s="19" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6105,6 +6105,123 @@
       </c>
       <c r="O97"/>
       <c r="P97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="163.5" customHeight="1" s="20">
+      <c r="A98" s="18">
+        <v>1804</v>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1856</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1804 – 1856</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikolaï NADEJDINE</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikola%C3%AF_Nadejdine" title=" Wikipedia"&gt;Nikolaï NADEJDINE&lt;/a&gt; est un critique littéraire, journaliste et philosophe russe. Né en 1804 dans la région de Riazan, fils de prêtre, il étudie à l’académie de théologie de Moscou, puis soutient en 1830 une thèse sur la poésie romantique. Professeur à l’université de Moscou, il y enseigne la théorie des beaux-arts et l’archéologie. Lecteur d’Oken et de &lt;a href="https://fr.wikipedia.org/wiki/Friedrich_Wilhelm_Joseph_von_Schelling" title=" Wikipedia"&gt;Schelling&lt;/a&gt;, il introduit en Russie une esthétique idéaliste : l’œuvre d’art est l’union d’une forme et d’une idée, qui en est l’âme.&lt;/p&gt; &lt;p&gt;Critique redouté, il juge sévèrement les premiers poèmes de Pouchkine, trop byroniens à ses yeux, mais salue son &lt;em&gt;Boris Godounov&lt;/em&gt;. Contre le romantisme, qu’il trouve sans racines, il veut une littérature qui exprime la conscience du peuple russe : pour lui, la littérature est l’une des forces qui conduisent une nation vers son propre développement. En 1831, il fonde la revue &lt;em&gt;Le Télescope&lt;/em&gt;, où débute le critique Vissarion Belinski, qui deviendra le maître de toute une génération. La revue fait connaître au public russe les débats philosophiques allemands.&lt;/p&gt; &lt;p&gt;En 1836, il publie dans &lt;em&gt;Le Télescope&lt;/em&gt; la première des &lt;em&gt;Lettres philosophiques&lt;/em&gt; de &lt;a href="https://fr.wikipedia.org/wiki/Piotr_Tchaada%C3%AFev" title=" Wikipedia"&gt;Tchaadaïev&lt;/a&gt;, qui affirme que la Russie n’a rien apporté à l’humanité. Le scandale est immense : la revue est fermée, Tchaadaïev déclaré fou, et Nadejdine exilé dans le Nord, à Oust-Syssolsk. Revenu deux ans plus tard, il se consacre à l’histoire, à la géographie et à l’ethnographie, et participe à la fondation de la Société russe de géographie. Il meurt à Saint-Pétersbourg en 1856.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H98" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/nadejdine-mini.webp</t>
+        </is>
+      </c>
+      <c r="J98" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esthetique ; metaphysique</t>
+        </is>
+      </c>
+      <c r="K98" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Idéalisme ; Romantisme</t>
+        </is>
+      </c>
+      <c r="L98" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">critique et philosophe russe, éditeur du Télescope, exilé pour avoir publié Tchaadaïev.</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O98"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="163.5" customHeight="1" s="20">
+      <c r="A99" s="18">
+        <v>1896</v>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1982</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1896 – 1982</t>
+        </is>
+      </c>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Roman JAKOBSON</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roman_Jakobson" title=" Wikipedia"&gt;Roman JAKOBSON&lt;/a&gt; est un linguiste et théoricien de la littérature russe, puis américain, l’un des fondateurs du &lt;a href="https://fr.wikipedia.org/wiki/Structuralisme" title=" Wikipedia"&gt;structuralisme&lt;/a&gt;. Né à Moscou en 1896 dans une famille juive aisée, il fonde en 1915 le Cercle linguistique de Moscou et participe au formalisme russe, qui étudie la littérature à partir de ce qui fait la spécificité d’un texte poétique. Ami des poètes futuristes, comme Maïakovski et Khlebnikov, il s’installe en 1920 en Tchécoslovaquie, où il soutient sa thèse et enseigne à l’université de Brno.&lt;/p&gt; &lt;p&gt;En 1926, il fonde avec Nikolaï Troubetskoï le Cercle linguistique de Prague. Prolongeant Saussure, il fonde la phonologie : une langue n’est pas une collection de sons, mais un système d’oppositions, où chaque son se définit par ce qui le distingue des autres. Fuyant le nazisme en 1939, il passe par la Scandinavie avant de gagner New York en 1941. Il y rencontre &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss" title=" Wikipedia"&gt;Claude Lévi-Strauss&lt;/a&gt;, à qui il fait découvrir la linguistique structurale : c’est de cette rencontre que naît l’anthropologie structurale, puis tout le mouvement structuraliste en France.&lt;/p&gt; &lt;p&gt;Professeur à Harvard et au MIT, il distingue en 1960 six fonctions du langage, selon que le message est tourné vers le monde dont il parle, vers celui qui parle, vers celui qui écoute, vers le contact, vers le code lui-même ou vers sa propre forme, ce qui définit la fonction poétique. Il montre aussi que la métaphore et la métonymie sont les deux grands pôles du langage, que l’aphasie peut toucher séparément. Il meurt à Cambridge, dans le Massachusetts, en 1982.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/jakobson-mini.webp</t>
+        </is>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">langage ; esthetique</t>
+        </is>
+      </c>
+      <c r="K99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structuralisme</t>
+        </is>
+      </c>
+      <c r="L99" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linguiste russe puis américain, l’un des fondateurs du structuralisme, théoricien des fonctions du langage.</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe ; juive</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="O99"/>
+      <c r="P99" t="inlineStr">
         <is>
           <t xml:space="preserve">Russe</t>
         </is>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E12" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vasily_Karpov_(philosophe)"  title=" Wikipedia"&gt;Vassili KARPOV&lt;/a&gt; était un philosophe et traducteur russe, figure importante de la philosophie académique chrétienne orthodoxe dans la Russie du XIXe siècle. Professeur à l'Académie théologique de Saint-Pétersbourg, il fut l'un des premiers traducteurs russes de Platon et contribua de manière decisive à l'introduction du platonisme dans la philosophie orthodoxe russe. Sa traduction des dialogues platoniciens — parue en plusieurs volumes entre 1840 et 1879 — resta longtemps la référence standard pour les lecteurs russes.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans son &lt;em&gt;Introduction à la philosophie&lt;/em&gt; (1840) et dans ses cours académiques, cherche à intégrer les acquis de la philosophie occidentale moderne — notamment l'idéalisme allemand de Kant et Schelling — dans le cadre d'une apologétique chrétienne orthodoxe. Contre le matérialisme et le sensualisme qui dominaient la philosophie naturaliste de son époque, il défend le caractère irréductible de la conscience spirituelle et la nécessité de la foi comme fondement d'une connaissance complète de la réalité. Sa conception du rapport entre foi et raison s'inscrit dans la grande tradition de la théologie orthodoxe.&lt;/p&gt;&lt;p&gt;Son influence sur le développement de la philosophie religieuse russe fut significative : il forma plusieurs générations d'étudiants dans les académies théologiques et contribua à établir un dialogue entre la tradition philosophique occidentale et la spiritualité orthodoxe russe. Bien que moins connu que ses successeurs Soloviev, Florenski ou Boulgakov, il représente un maillon essentiel dans la chaîne de transmission du platonisme chrétien en Russie. Sa traduction de Platon reste sa contribution la plus durable.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ru.wikipedia.org/wiki/Карпов,_Василий_Николаевич"  title=" Wikipedia"&gt;Vassili KARPOV&lt;/a&gt; était un philosophe et traducteur russe, figure importante de la philosophie académique chrétienne orthodoxe dans la Russie du XIXe siècle. Professeur à l'Académie théologique de Saint-Pétersbourg, il fut l'un des premiers traducteurs russes de Platon et contribua de manière decisive à l'introduction du platonisme dans la philosophie orthodoxe russe. Sa traduction des dialogues platoniciens — parue en plusieurs volumes entre 1840 et 1879 — resta longtemps la référence standard pour les lecteurs russes.&lt;/p&gt;&lt;p&gt;Sa philosophie, exposée dans son &lt;em&gt;Introduction à la philosophie&lt;/em&gt; (1840) et dans ses cours académiques, cherche à intégrer les acquis de la philosophie occidentale moderne — notamment l'idéalisme allemand de Kant et Schelling — dans le cadre d'une apologétique chrétienne orthodoxe. Contre le matérialisme et le sensualisme qui dominaient la philosophie naturaliste de son époque, il défend le caractère irréductible de la conscience spirituelle et la nécessité de la foi comme fondement d'une connaissance complète de la réalité. Sa conception du rapport entre foi et raison s'inscrit dans la grande tradition de la théologie orthodoxe.&lt;/p&gt;&lt;p&gt;Son influence sur le développement de la philosophie religieuse russe fut significative : il forma plusieurs générations d'étudiants dans les académies théologiques et contribua à établir un dialogue entre la tradition philosophique occidentale et la spiritualité orthodoxe russe. Bien que moins connu que ses successeurs Soloviev, Florenski ou Boulgakov, il représente un maillon essentiel dans la chaîne de transmission du platonisme chrétien en Russie. Sa traduction de Platon reste sa contribution la plus durable.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H12" s="19" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="E21" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Constantin_Aksakov" title=" Wikipedia"&gt;Constantin AKSAKOV&lt;/a&gt; était un philosophe, historien et publiciste russe, l'un des principaux théoriciens du slavophilisme et fils du célèbre écrivain Sergueï Aksakov. Élève de Hegel à travers le cercle Stankevitch, il évolua vers &lt;a href="https://fr.wikipedia.org/wiki/Slavophilisme/" title="slavophilisme par wikipedia"&gt; un slavophilisme radical &lt;/a&gt; qui le distingue de la modération relative de Khomiakov ou Kireïevski. Sa philosophie de l'histoire oppose radicalement le peuple russe (narod), porteur de valeurs communautaires, spirituelles et non-étatiques, à l'État occidental fondé sur la contrainte et la violence.&lt;/p&gt;&lt;p&gt;Sa thèse philosophique centrale, développée dans ses &lt;em&gt;Notes sur l'histoire de la Russie ancienne&lt;/em&gt; et ses articles des années 1850-1860, soutient que le peuple russe, à la différence des peuples occidentaux, n'a jamais aspiré au pouvoir politique mais a toujours cherché à vivre dans la « terre », communauté organique d'amour et de liberté intérieure. L'État est un mal nécessaire, accepté librement par le peuple pour assurer la paix extérieure, mais distinct de la vie profonde du pays. Cette distinction terre/État allait devenir un thème central de la pensée politique russe.&lt;/p&gt;&lt;p&gt;Sa philosophie du langage, exposée dans ses études sur la grammaire russe, reflète également ses convictions slavophiles : le russe, langue du peuple, est porteur d'une vision du monde organique et communautaire supérieure à la rationalité desséchante de l'Occident.   &lt;a href="https://oursmagazine.fr/culture-russe/ecrivains/constantin-aksakov/" title="biographie de constantin aksakov par oursmagazine"&gt; Son ardeur polémique, &lt;/a&gt;  son refus de tout compromis avec le libéralisme et son attachement romantique à l'idéal de la commune paysanne font de lui le slavophile le plus intransigeant et le plus cohérent. Mort jeune, à 43 ans, il laissa une œuvre fragmentaire mais stimulante.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Constantin_Aksakov" title=" Wikipedia"&gt;Constantin AKSAKOV&lt;/a&gt; était un philosophe, historien et publiciste russe, l'un des principaux théoriciens du slavophilisme et fils du célèbre écrivain Sergueï Aksakov. Élève de Hegel à travers le cercle Stankevitch, il évolua vers &lt;a href="https://fr.wikipedia.org/wiki/Slavophilisme" title="slavophilisme par wikipedia"&gt; un slavophilisme radical &lt;/a&gt; qui le distingue de la modération relative de Khomiakov ou Kireïevski. Sa philosophie de l'histoire oppose radicalement le peuple russe (narod), porteur de valeurs communautaires, spirituelles et non-étatiques, à l'État occidental fondé sur la contrainte et la violence.&lt;/p&gt;&lt;p&gt;Sa thèse philosophique centrale, développée dans ses &lt;em&gt;Notes sur l'histoire de la Russie ancienne&lt;/em&gt; et ses articles des années 1850-1860, soutient que le peuple russe, à la différence des peuples occidentaux, n'a jamais aspiré au pouvoir politique mais a toujours cherché à vivre dans la « terre », communauté organique d'amour et de liberté intérieure. L'État est un mal nécessaire, accepté librement par le peuple pour assurer la paix extérieure, mais distinct de la vie profonde du pays. Cette distinction terre/État allait devenir un thème central de la pensée politique russe.&lt;/p&gt;&lt;p&gt;Sa philosophie du langage, exposée dans ses études sur la grammaire russe, reflète également ses convictions slavophiles : le russe, langue du peuple, est porteur d'une vision du monde organique et communautaire supérieure à la rationalité desséchante de l'Occident.   &lt;a href="https://oursmagazine.fr/culture-russe/ecrivains/constantin-aksakov/" title="biographie de constantin aksakov par oursmagazine"&gt; Son ardeur polémique, &lt;/a&gt;  son refus de tout compromis avec le libéralisme et son attachement romantique à l'idéal de la commune paysanne font de lui le slavophile le plus intransigeant et le plus cohérent. Mort jeune, à 43 ans, il laissa une œuvre fragmentaire mais stimulante.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="E48" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikolai_Kare%C3%AFev" title=" Wikipedia"&gt;Nikolaï KAREÏEV&lt;/a&gt; était un historien et philosophe de l'histoire russe, l'un des fondateurs de la science historique moderne en Russie et un représentant important du  &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title="positivisme par wikipedia"&gt;positivisme historique. &lt;/a&gt;  Professeur à l'Université de Saint-Pétersbourg pendant des décennies, il forma plusieurs générations d'historiens russes et contribua de manière décisive à la professionnalisation de la discipline historique en Russie. Ses travaux sur l'histoire de la France paysanne au XVIIIe siècle et sur la Révolution française furent longtemps des références incontournables.&lt;/p&gt;&lt;p&gt;Sa  &lt;a href="https://www.persee.fr/doc/ahrf_0003-4436_1979_num_237_1_1045" title="historiens russes de la revolution française par persee"&gt;philosophie de l'histoire, &lt;/a&gt;  exposée dans son ouvrage fondamental &lt;em&gt;Les Fondements de la philosophie de l'histoire&lt;/em&gt; (1883), cherche à définir les bases théoriques et méthodologiques de la science historique. Influencé par Comte, Mill et Spencer, mais aussi par la tradition populiste russe (Lavrov, Mikhaïlovski), il développe une philosophie de l'histoire qui combine l'explication objective des phénomènes sociaux avec une dimension normative : l'histoire humaine a un sens qui est le progrès de la liberté et de la personnalité. Sa méthode socio-historique distingue les facteurs psychologiques (volontés et consciences individuelles) et les facteurs sociaux (structures objectives) dans l'explication historique.&lt;/p&gt;&lt;p&gt;Ses travaux sur la Révolution française — &lt;em&gt;Les Paysans et la question paysanne en France dans le dernier quart du XVIIIe siècle&lt;/em&gt; (1879) — constituent une contribution pionnière à l'histoire sociale. Libéral modéré, il soutint les réformes constitutionnelles de 1905 et la démocratie représentative. Son œuvre philosophique et historiographique, bien que moins connue que celle de ses contemporains plus célèbres, représente un moment important du développement de la pensée historique russe à l'intersection du positivisme et du libéralisme.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nikolai_Ivanovich_Kareev" title=" Wikipedia"&gt;Nikolaï KAREÏEV&lt;/a&gt; était un historien et philosophe de l'histoire russe, l'un des fondateurs de la science historique moderne en Russie et un représentant important du  &lt;a href="https://fr.wikipedia.org/wiki/Positivisme" title="positivisme par wikipedia"&gt;positivisme historique. &lt;/a&gt;  Professeur à l'Université de Saint-Pétersbourg pendant des décennies, il forma plusieurs générations d'historiens russes et contribua de manière décisive à la professionnalisation de la discipline historique en Russie. Ses travaux sur l'histoire de la France paysanne au XVIIIe siècle et sur la Révolution française furent longtemps des références incontournables.&lt;/p&gt;&lt;p&gt;Sa  &lt;a href="https://www.persee.fr/doc/ahrf_0003-4436_1979_num_237_1_1045" title="historiens russes de la revolution française par persee"&gt;philosophie de l'histoire, &lt;/a&gt;  exposée dans son ouvrage fondamental &lt;em&gt;Les Fondements de la philosophie de l'histoire&lt;/em&gt; (1883), cherche à définir les bases théoriques et méthodologiques de la science historique. Influencé par Comte, Mill et Spencer, mais aussi par la tradition populiste russe (Lavrov, Mikhaïlovski), il développe une philosophie de l'histoire qui combine l'explication objective des phénomènes sociaux avec une dimension normative : l'histoire humaine a un sens qui est le progrès de la liberté et de la personnalité. Sa méthode socio-historique distingue les facteurs psychologiques (volontés et consciences individuelles) et les facteurs sociaux (structures objectives) dans l'explication historique.&lt;/p&gt;&lt;p&gt;Ses travaux sur la Révolution française — &lt;em&gt;Les Paysans et la question paysanne en France dans le dernier quart du XVIIIe siècle&lt;/em&gt; (1879) — constituent une contribution pionnière à l'histoire sociale. Libéral modéré, il soutint les réformes constitutionnelles de 1905 et la démocratie représentative. Son œuvre philosophique et historiographique, bien que moins connue que celle de ses contemporains plus célèbres, représente un moment important du développement de la pensée historique russe à l'intersection du positivisme et du libéralisme.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev_(philosophe)https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion&lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion&lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://ru.wikipedia.org/wiki/Огнёв,_Александр_Александрович"  title=" Wikipedia (ru)"&gt;Alexandre OGNIOV&lt;/a&gt; était un philosophe russe, représentant du courant de l'intuitivisme réaliste dans la philosophie russe du début du XXe siècle. Comme Boldyrev, il s'inscrivait dans la mouvance de Nicolas Lossky et cherchait à développer une théorie réaliste de la connaissance fondée sur l'intuition directe de la réalité.&lt;/p&gt;&lt;p&gt;Sa contribution philosophique, développée dans des articles et des essais publiés dans les revues philosophiques russes des années 1900-1910, portait principalement sur les fondements de la logique et de la théorie de la connaissance. Dans le cadre de &lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title="intuitivisme par wikipedia"&gt;l'intuitivisme réaliste, &lt;/a&gt;il explorait les conditions de possibilité de la connaissance objective, cherchant à montrer comment l'esprit humain peut saisir la structure logique de la réalité sans se limiter aux phénomènes subjectifs. Sa réflexion sur le rapport entre logique formelle et intuition métaphysique constitue une contribution originale aux débats épistémologiques de son époque.&lt;/p&gt;&lt;p&gt;La relative obscurité d'Ogniov dans l'histoire de la philosophie russe tient en partie à l'interruption brutale que la révolution bolchevique et la guerre civile imposèrent à la vie philosophique russe. Mort en 1925, il appartient à cette génération de philosophes russes dont l'œuvre fut interrompue ou déformée par les convulsions de l'histoire. Ses travaux méritent néanmoins d'être connus comme témoignage des débats philosophiques rigoureux qui animaient les cercles philosophiques russes des premières décennies du XXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://ru.wikipedia.org/wiki/Огнёв,_Александр_Иванович"  title=" Wikipedia (ru)"&gt;Alexandre OGNIOV&lt;/a&gt; était un philosophe russe, représentant du courant de l'intuitivisme réaliste dans la philosophie russe du début du XXe siècle. Comme Boldyrev, il s'inscrivait dans la mouvance de Nicolas Lossky et cherchait à développer une théorie réaliste de la connaissance fondée sur l'intuition directe de la réalité.&lt;/p&gt;&lt;p&gt;Sa contribution philosophique, développée dans des articles et des essais publiés dans les revues philosophiques russes des années 1900-1910, portait principalement sur les fondements de la logique et de la théorie de la connaissance. Dans le cadre de &lt;a href="https://fr.wikipedia.org/wiki/Intuitivisme"  title="intuitivisme par wikipedia"&gt;l'intuitivisme réaliste, &lt;/a&gt;il explorait les conditions de possibilité de la connaissance objective, cherchant à montrer comment l'esprit humain peut saisir la structure logique de la réalité sans se limiter aux phénomènes subjectifs. Sa réflexion sur le rapport entre logique formelle et intuition métaphysique constitue une contribution originale aux débats épistémologiques de son époque.&lt;/p&gt;&lt;p&gt;La relative obscurité d'Ogniov dans l'histoire de la philosophie russe tient en partie à l'interruption brutale que la révolution bolchevique et la guerre civile imposèrent à la vie philosophique russe. Mort en 1925, il appartient à cette génération de philosophes russes dont l'œuvre fut interrompue ou déformée par les convulsions de l'histoire. Ses travaux méritent néanmoins d'être connus comme témoignage des débats philosophiques rigoureux qui animaient les cercles philosophiques russes des premières décennies du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H77" s="19" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikolai_Setnitsky"  title=" Wikipedia"&gt;Nikolaï SETNITSKI&lt;/a&gt; était un économiste, philosophe et cosmiste russe, l'un des principaux continuateurs et diffuseurs de la pensée de Nikolaï Fedorov dans les premières décennies soviétiques. Collaborant étroitement avec Aleksandre Gorski, il publia des études sur Fedorov et des &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_46_1_1165" title="la philosophie du cosmisme russe par persée"&gt;textes cosmistes &lt;/a&gt; dans les années 1920-1930, tentant d'intégrer l'utopisme cosmiste dans le cadre du projet soviétique de transformation radicale de la réalité.&lt;/p&gt;&lt;p&gt;Sa contribution philosophique principale porte sur l'articulation entre l'économie et la philosophie cosmiste. Dans ses travaux — notamment &lt;em&gt;La Question capitaliste et l'économie mondiale&lt;/em&gt; (1926) et ses essais sur Fedorov — il cherche à montrer que la crise du capitalisme mondial peut être surmontée non par le simple socialisme économique mais par un projet de régulation consciente de l'ensemble du cosmos, incluant la maîtrise des forces naturelles (météorologie, agriculture scientifique, énergie cosmique) et la résurrection des ancêtres. Cette synthèse d'économie politique et de cosmisme religieux est l'une des expressions les plus originales du fedorovianisme du XXe siècle.&lt;/p&gt;&lt;p&gt;Ses travaux sur Dostoïevski et sur la signification cosmiste de l'œuvre littéraire russe témoignent d'une culture philosophique et littéraire étendue. Arrêté par les autorités soviétiques en 1936, condamné à mort et fusillé en 1937, il fut l'une des victimes de la répression stalinienne contre les milieux intellectuels. Sa courte biographie, entre utopie cosmiste et terreur soviétique, illustre de manière saisissante les contradictions et les tragédies de l'intelligentsia russe du XXe siècle.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nikolaï_Setnitski"  title=" Wikipedia"&gt;Nikolaï SETNITSKI&lt;/a&gt; était un économiste, philosophe et cosmiste russe, l'un des principaux continuateurs et diffuseurs de la pensée de Nikolaï Fedorov dans les premières décennies soviétiques. Collaborant étroitement avec Aleksandre Gorski, il publia des études sur Fedorov et des &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2018_num_46_1_1165" title="la philosophie du cosmisme russe par persée"&gt;textes cosmistes &lt;/a&gt; dans les années 1920-1930, tentant d'intégrer l'utopisme cosmiste dans le cadre du projet soviétique de transformation radicale de la réalité.&lt;/p&gt;&lt;p&gt;Sa contribution philosophique principale porte sur l'articulation entre l'économie et la philosophie cosmiste. Dans ses travaux — notamment &lt;em&gt;La Question capitaliste et l'économie mondiale&lt;/em&gt; (1926) et ses essais sur Fedorov — il cherche à montrer que la crise du capitalisme mondial peut être surmontée non par le simple socialisme économique mais par un projet de régulation consciente de l'ensemble du cosmos, incluant la maîtrise des forces naturelles (météorologie, agriculture scientifique, énergie cosmique) et la résurrection des ancêtres. Cette synthèse d'économie politique et de cosmisme religieux est l'une des expressions les plus originales du fedorovianisme du XXe siècle.&lt;/p&gt;&lt;p&gt;Ses travaux sur Dostoïevski et sur la signification cosmiste de l'œuvre littéraire russe témoignent d'une culture philosophique et littéraire étendue. Arrêté par les autorités soviétiques en 1936, condamné à mort et fusillé en 1937, il fut l'une des victimes de la répression stalinienne contre les milieux intellectuels. Sa courte biographie, entre utopie cosmiste et terreur soviétique, illustre de manière saisissante les contradictions et les tragédies de l'intelligentsia russe du XXe siècle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H81" s="19" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dmitri_Pissarev" title=" Wikipedia"&gt;Dmitri PISSAREV&lt;/a&gt; était un critique littéraire et philosophe russe, la figure la plus radicale du nihilisme russe des années 1860. Emprisonné pendant quatre ans dans la forteresse Pierre-et-Paul (1862-1866) pour ses écrits révolutionnaires, il y rédigea ses principaux essais critiques et philosophiques avant de mourir noyé à 27 ans. Sa courte carrière et sa mort prématurée en firent une &lt;a href="https://www.youtube.com/watch?v=yNMHb20AgXI"  title="le nihilisme russe par europe through the ages"&gt;figure mythique de l'intelligentsia&lt;/a&gt;  radicale russe.&lt;/p&gt;&lt;p&gt;Sa philosophie est un matérialisme et un utilitarisme radical tirant les conséquences les plus  &lt;a href="https://www.persee.fr/doc/slave_0080-2557_1946_num_22_1_1436"  title="le nihilisme pisarev par persée"&gt;extrêmes du nihilisme : &lt;/a&gt; si Dieu n'existe pas et si l'homme est un être naturel gouverné par ses intérêts, alors toute la culture, l'art, la philosophie et la morale traditionnelles n'ont de valeur que dans la mesure où elles contribuent au bien-être matériel de l'humanité. Sa célèbre formule — « une paire de bottes vaut mieux que Shakespeare » — résume cette esthétique utilitariste radicale. Dans ses essais sur la critique littéraire, il soumettait les œuvres littéraires au test de leur utilité sociale.&lt;/p&gt;&lt;p&gt;Sa polémique avec Pisemski, Tourgueniev et Dostoïevski — notamment sa critique des &lt;em&gt;Pères et fils&lt;/em&gt; de Tourgueniev — constitue un document important du débat culturel des années 1860 en Russie. Paradoxalement, Pissarev admirait les sciences naturelles et le travail des scientifiques comme Faraday et Darwin, voyant dans la science positive le seul instrument d'émancipation réelle de l'humanité. Sa pensée, à la fois brutalement réductrice et sincèrement utopique, incarne les contradictions et la passion de toute une génération de nihilistes russes pour qui la destruction des illusions était le premier pas vers la libération.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dmitri_Pissarev" title=" Wikipedia"&gt;Dmitri PISSAREV&lt;/a&gt; était un critique littéraire et philosophe russe, la figure la plus radicale du nihilisme russe des années 1860. Emprisonné pendant quatre ans dans la forteresse Pierre-et-Paul (1862-1866) pour ses écrits révolutionnaires, il y rédigea ses principaux essais critiques et philosophiques avant de mourir noyé à 27 ans. Sa courte carrière et sa mort prématurée en firent une figure mythique de l'intelligentsia  radicale russe.&lt;/p&gt;&lt;p&gt;Sa philosophie est un matérialisme et un utilitarisme radical tirant les conséquences les plus  &lt;a href="https://www.persee.fr/doc/slave_0080-2557_1946_num_22_1_1436"  title="le nihilisme pisarev par persée"&gt;extrêmes du nihilisme : &lt;/a&gt; si Dieu n'existe pas et si l'homme est un être naturel gouverné par ses intérêts, alors toute la culture, l'art, la philosophie et la morale traditionnelles n'ont de valeur que dans la mesure où elles contribuent au bien-être matériel de l'humanité. Sa célèbre formule — « une paire de bottes vaut mieux que Shakespeare » — résume cette esthétique utilitariste radicale. Dans ses essais sur la critique littéraire, il soumettait les œuvres littéraires au test de leur utilité sociale.&lt;/p&gt;&lt;p&gt;Sa polémique avec Pisemski, Tourgueniev et Dostoïevski — notamment sa critique des &lt;em&gt;Pères et fils&lt;/em&gt; de Tourgueniev — constitue un document important du débat culturel des années 1860 en Russie. Paradoxalement, Pissarev admirait les sciences naturelles et le travail des scientifiques comme Faraday et Darwin, voyant dans la science positive le seul instrument d'émancipation réelle de l'humanité. Sa pensée, à la fois brutalement réductrice et sincèrement utopique, incarne les contradictions et la passion de toute une génération de nihilistes russes pour qui la destruction des illusions était le premier pas vers la libération.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E66" s="25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Bogdanov"  title=" Wikipedia"&gt;Alexandre BOGDANOV&lt;/a&gt; était un philosophe, médecin, économiste et théoricien politique russe, figure à la fois centrale et marginalisée de la pensée révolutionnaire du début du XXe siècle. Il fut l'un des proches collaborateurs de Lénine au sein du Parti bolchévique, avant d'en être exclu en 1909 en raison de ses positions philosophiques jugées incompatibles avec le matérialisme orthodoxe. Lénine lui consacra une réfutation sévère dans &lt;em&gt;Matérialisme et empiriocriticisme&lt;/em&gt;. Bogdanov avait en effet développé une philosophie originale, &lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Empiriomonisme par wikipedia"&gt;l'« empiriomonisme », &lt;/a&gt; synthèse de l'empiriocriticisme de Mach et du marxisme, qui refusait la distinction entre matière et esprit au profit d'une expérience unifiée.&lt;/p&gt;&lt;p&gt;Sa contribution intellectuelle la plus durable est la &lt;em&gt;Tektologie&lt;/em&gt; (1913-1922), une « science universelle de l'organisation » dans laquelle il cherchait à dégager les lois communes à toute forme d'organisation — biologique, sociale, économique, physique. Ce projet anticipait de façon remarquable la cybernétique de Norbert Wiener, la théorie générale des systèmes de Ludwig von Bertalanffy et la pensée de la complexité. Il fonda également en 1918 le Proletkult, organisation culturelle visant à créer une culture prolétarienne autonome, indépendante de l'État. Son roman de science-fiction &lt;em&gt;Étoile rouge&lt;/em&gt; (1908) imagine une société martienne socialiste utopique, préfigurant des thèmes qui allaient occuper toute la littérature soviétique de science-fiction.&lt;/p&gt;&lt;p&gt;Il mourut en 1928 lors d'une expérience de  &lt;a href="https://www.youtube.com/watch?v=0D40y81fINI"  title="hematologist alexandezr bogdanov par together rf"&gt;transfusion sanguine &lt;/a&gt; sur lui-même — il était aussi pionnier de la médecine transfusionnelle et dirigeait l'Institut de transfusion sanguine de Moscou. Cette mort étrange, qui mêle engagement scientifique et utopie du  &lt;a href="https://www.persee.fr/doc/dreso_0769-3362_1994_num_28_1_1293"  title="transfusion sanguine et immortalité par persée"&gt;renouveau biologique, &lt;/a&gt; illustre la cohérence profonde d'une pensée qui cherchait à transformer à la fois l'organisation sociale et la nature humaine. Sa réhabilitation intellectuelle, tardive, est aujourd'hui en cours dans les milieux des théories des systèmes et de la complexité.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_Bogdanov"  title=" Wikipedia"&gt;Alexandre BOGDANOV&lt;/a&gt; était un philosophe, médecin, économiste et théoricien politique russe, figure à la fois centrale et marginalisée de la pensée révolutionnaire du début du XXe siècle. Il fut l'un des proches collaborateurs de Lénine au sein du Parti bolchévique, avant d'en être exclu en 1909 en raison de ses positions philosophiques jugées incompatibles avec le matérialisme orthodoxe. Lénine lui consacra une réfutation sévère dans &lt;em&gt;Matérialisme et empiriocriticisme&lt;/em&gt;. Bogdanov avait en effet développé une philosophie originale, &lt;a href="https://fr.wikipedia.org/wiki/Empiriomonisme"  title="Empiriomonisme par wikipedia"&gt;l'« empiriomonisme », &lt;/a&gt; synthèse de l'empiriocriticisme de Mach et du marxisme, qui refusait la distinction entre matière et esprit au profit d'une expérience unifiée.&lt;/p&gt;&lt;p&gt;Sa contribution intellectuelle la plus durable est la &lt;em&gt;Tektologie&lt;/em&gt; (1913-1922), une « science universelle de l'organisation » dans laquelle il cherchait à dégager les lois communes à toute forme d'organisation — biologique, sociale, économique, physique. Ce projet anticipait de façon remarquable la cybernétique de Norbert Wiener, la théorie générale des systèmes de Ludwig von Bertalanffy et la pensée de la complexité. Il fonda également en 1918 le Proletkult, organisation culturelle visant à créer une culture prolétarienne autonome, indépendante de l'État. Son roman de science-fiction &lt;em&gt;Étoile rouge&lt;/em&gt; (1908) imagine une société martienne socialiste utopique, préfigurant des thèmes qui allaient occuper toute la littérature soviétique de science-fiction.&lt;/p&gt;&lt;p&gt;Il mourut en 1928 lors d'une expérience de  transfusion sanguine  sur lui-même — il était aussi pionnier de la médecine transfusionnelle et dirigeait l'Institut de transfusion sanguine de Moscou. Cette mort étrange, qui mêle engagement scientifique et utopie du  &lt;a href="https://www.persee.fr/doc/dreso_0769-3362_1994_num_28_1_1293"  title="transfusion sanguine et immortalité par persée"&gt;renouveau biologique, &lt;/a&gt; illustre la cohérence profonde d'une pensée qui cherchait à transformer à la fois l'organisation sociale et la nature humaine. Sa réhabilitation intellectuelle, tardive, est aujourd'hui en cours dans les milieux des théories des systèmes et de la complexité.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F66" s="18" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -3325,56 +3325,51 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="261.15" customHeight="1" s="20">
+    <row r="50" ht="261.9" customHeight="1" s="20">
       <c r="A50" s="18" t="n">
         <v>1853</v>
       </c>
       <c r="B50" s="18" t="n">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>1853 – 1900</t>
+          <t>1853 – 1904</t>
         </is>
       </c>
       <c r="D50" s="18" t="inlineStr">
         <is>
-          <t>Vladimir SOLOVIEV</t>
-        </is>
-      </c>
-      <c r="E50" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion&lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="18" t="inlineStr">
-        <is>
-          <t>00-AdbJIkvs</t>
-        </is>
-      </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>vladimir soloviev par the throught table</t>
+          <t>Nikolaï KORKUNOV</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nikolai_Korkunov" title=" Wikipedia"&gt;Nikolaï KORKUNOV&lt;/a&gt; était un juriste et philosophe du droit russe, l'un des penseurs les plus importants de la philosophie juridique en Russie à la fin du XIXe siècle. Professeur à l'École de droit de Saint-Pétersbourg et à l'Université impériale, il fut l'un des premiers à introduire en Russie une approche systématique et philosophique du droit public, fondée sur des bases positivistes et sociologiques. Ses manuels de droit constitutionnel comparé et de théorie générale du droit furent des ouvrages de référence pour plusieurs générations de juristes russes.&lt;/p&gt;&lt;p&gt;Sa &lt;a href="https://grokipedia.com/page/nikolai_korkunov" titre="nikolai korkunov par grokipedia "&gt;contribution philosophique &lt;/a&gt; principale est sa théorie positiviste du droit, exposée dans ses &lt;em&gt;Conférences sur la théorie générale du droit&lt;/em&gt; (1886, nombreuses éditions). Contre le jusnaturalisme qui fonde le droit sur des principes moraux transcendants, et contre le positivisme juridique formaliste qui réduit le droit aux seules normes en vigueur, il développe une conception sociologique du droit : le droit est le moyen par lequel la société différencie les intérêts en conflits et organise leur coexistence. Cette approche, nourrie de Spencer et des sociologues positivistes, contribua à établir la sociologie juridique comme discipline autonome en Russie.&lt;/p&gt;&lt;p&gt;Son livre &lt;em&gt;Le Droit international&lt;/em&gt; (1886) et ses travaux sur le droit administratif témoignent d'une maîtrise encyclopédique du droit public comparé. Sa philosophie juridique, qui insistait sur le caractère social et historique du droit contre toute conception abstraite, prépara le terrain pour les développements ultérieurs de la sociologie juridique russe et soviétique. Korkounov représente l'importation réussie du positivisme juridique européen dans la tradition juridique russe, adaptée aux conditions spécifiques de l'Empire russe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/vsoloviev-mini.webp</t>
+          <t>https://www.laphilo.fr/pho/nkorkunov-mini.webp</t>
+        </is>
+      </c>
+      <c r="I50" s="19" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/photo/nkorkunov.webp</t>
         </is>
       </c>
       <c r="J50" s="19" t="inlineStr">
         <is>
-          <t>metaphysique ; spiritualite</t>
+          <t>politique</t>
         </is>
       </c>
       <c r="K50" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Sophiologie ; Oecuménisme</t>
+          <t>Positivisme</t>
         </is>
       </c>
       <c r="L50" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe, poète et théologien russe, figure de la philosophie religieuse du XIXe.</t>
+          <t xml:space="preserve"> philosophe du droit russe,  penseur de la philosophie juridique russe.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3382,61 +3377,66 @@
           <t xml:space="preserve">russe</t>
         </is>
       </c>
-      <c r="O50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" ht="261.9" customHeight="1" s="20">
+    </row>
+    <row r="51" ht="261.15" customHeight="1" s="20">
       <c r="A51" s="18" t="n">
         <v>1853</v>
       </c>
       <c r="B51" s="18" t="n">
-        <v>1904</v>
+        <v>1900</v>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>1853 – 1904</t>
+          <t>1853 – 1900</t>
         </is>
       </c>
       <c r="D51" s="18" t="inlineStr">
         <is>
-          <t>Nikolaï KORKUNOV</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Nikolai_Korkunov" title=" Wikipedia"&gt;Nikolaï KORKUNOV&lt;/a&gt; était un juriste et philosophe du droit russe, l'un des penseurs les plus importants de la philosophie juridique en Russie à la fin du XIXe siècle. Professeur à l'École de droit de Saint-Pétersbourg et à l'Université impériale, il fut l'un des premiers à introduire en Russie une approche systématique et philosophique du droit public, fondée sur des bases positivistes et sociologiques. Ses manuels de droit constitutionnel comparé et de théorie générale du droit furent des ouvrages de référence pour plusieurs générations de juristes russes.&lt;/p&gt;&lt;p&gt;Sa &lt;a href="https://grokipedia.com/page/nikolai_korkunov" titre="nikolai korkunov par grokipedia "&gt;contribution philosophique &lt;/a&gt; principale est sa théorie positiviste du droit, exposée dans ses &lt;em&gt;Conférences sur la théorie générale du droit&lt;/em&gt; (1886, nombreuses éditions). Contre le jusnaturalisme qui fonde le droit sur des principes moraux transcendants, et contre le positivisme juridique formaliste qui réduit le droit aux seules normes en vigueur, il développe une conception sociologique du droit : le droit est le moyen par lequel la société différencie les intérêts en conflits et organise leur coexistence. Cette approche, nourrie de Spencer et des sociologues positivistes, contribua à établir la sociologie juridique comme discipline autonome en Russie.&lt;/p&gt;&lt;p&gt;Son livre &lt;em&gt;Le Droit international&lt;/em&gt; (1886) et ses travaux sur le droit administratif témoignent d'une maîtrise encyclopédique du droit public comparé. Sa philosophie juridique, qui insistait sur le caractère social et historique du droit contre toute conception abstraite, prépara le terrain pour les développements ultérieurs de la sociologie juridique russe et soviétique. Korkounov représente l'importation réussie du positivisme juridique européen dans la tradition juridique russe, adaptée aux conditions spécifiques de l'Empire russe.&lt;/p&gt;</t>
+          <t>Vladimir SOLOVIEV</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Vladimir_Soloviev" title=" Wikipedia"&gt;Vladimir SOLOVIEV&lt;/a&gt; était un philosophe, poète et théologien russe, la figure la plus importante de la philosophie religieuse russe du XIXe siècle et l'un des penseurs les plus originaux de son temps à l'échelle européenne. Fils de l'historien Sergueï Soloviev, il soutint sa thèse à 21 ans et acquit rapidement une renommée considérable, avant de se brouiller avec l'Université de Moscou en raison de ses positions philosophiques et politiques audacieuses. &lt;/p&gt; &lt;p&gt; Sa philosophie cherche à réaliser la  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1934_num_14_6_2921" title="métaphysique religieuse par persee"&gt;grande synthèse de la religion&lt;/a&gt;, de la philosophie et de la science qu'il appelle la « philosophie unifiée » ou « pan-unité ». Contre le positivisme qui sépare la raison de la foi, et contre le mysticisme qui rejette la raison, il défend l'idée que la vérité est une et que ses différentes approches — scientifique, philosophique et mystique — doivent être unifiées. Sa métaphysique de la pan-unité conçoit l'Absolu comme l'unité de tout ce qui est, et l'histoire comme le processus par lequel cette unité se réalise. &lt;/p&gt; &lt;p&gt;   &lt;a href="https://www.youtube.com/watch?v=8pZkMwlPKwo" title="vladimir soloviev par aneckcahap"&gt;Son concept de &lt;/a&gt; &lt;em&gt;Sofia&lt;/em&gt; (la Sagesse divine, principe féminin du monde) est l'une de ses contributions les plus originales et les plus discutées. Dans &lt;em&gt;La Justification du Bien&lt;/em&gt; (1897), il élabore une éthique fondée sur trois principes : la honte, la pitié et la vénération. Son œuvre poétique et ses &lt;em&gt;Trois Entretiens&lt;/em&gt; (1900) sur la fin des temps témoignent d'une dimension prophétique et littéraire remarquable. Dostoïevski et Tolstoï furent ses amis et interlocuteurs ; il influença profondément les symbolistes russes et toute la renaissance philosophique religieuse russe du début du XXe siècle. &lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>00-AdbJIkvs</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>vladimir soloviev par the throught table</t>
         </is>
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>https://www.laphilo.fr/pho/nkorkunov-mini.webp</t>
-        </is>
-      </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/photo/nkorkunov.webp</t>
+          <t>https://www.laphilo.fr/pho/vsoloviev-mini.webp</t>
         </is>
       </c>
       <c r="J51" s="19" t="inlineStr">
         <is>
-          <t>politique</t>
+          <t>metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K51" s="19" t="inlineStr">
         <is>
-          <t>Positivisme</t>
+          <t xml:space="preserve">Spiritualisme ; Sophiologie ; Oecuménisme</t>
         </is>
       </c>
       <c r="L51" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> philosophe du droit russe,  penseur de la philosophie juridique russe.</t>
+          <t xml:space="preserve"> philosophe, poète et théologien russe, figure de la philosophie religieuse du XIXe.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">russe</t>
         </is>
+      </c>
+      <c r="O51">
+        <v>3</v>
       </c>
     </row>
     <row r="52" ht="291" customHeight="1" s="20">
@@ -6328,9 +6328,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Nikola%C3%AF_Grot&quot; title=&quot; Wikipedia&quot;&gt;Nikolaï GROT&lt;/a&gt; était un philosophe et psychologue russe, fondateur de la principale revue philosophique russe de la fin du XIXe siècle et animateur inlassable de la vie philosophique institutionnelle en Russie. Professeur à l'Université de Moscou, il fonda en 1889 la Société psychologique de Moscou et la revue &lt;em&gt;Voprosy filosofii i psikhologii&lt;/em&gt; (Questions de philosophie et de psychologie), qui devint le principal forum de la pensée philosophique russe jusqu'à la révolution de 1917 et publia les œuvres de Soloviev, Tolstoï, Troubetskoï et de nombreux autres penseurs majeurs.&lt;/p&gt;&lt;p&gt;Sa philosophie personnelle, exposée dans ses travaux sur la psychologie et la théorie de la connaissance, évolua du positivisme de jeunesse vers un idéalisme de plus en plus marqué. Sa &lt;em&gt;Psychologie des émotions&lt;/em&gt; (1879-1880) cherchait à fonder une psychologie scientifique des processus affectifs. Dans ses travaux ultérieurs, notamment &lt;em&gt;Sur la liberté de la volonté&lt;/em&gt; (1889), il développa une philosophie du moi et de la liberté qui le rapprochait des traditions idéalistes et spiritualistes. Sa réflexion sur les fondements de la morale et sur le rapport entre la science et les valeurs constitue une contribution intéressante au débat épistémologique de son époque.&lt;/p&gt;&lt;p&gt;Son rôle institutionnel — fondateur de la société philosophique et de la revue — fut sans doute plus important que sa contribution doctrinale propre. En créant un espace de dialogue entre les différentes tendances de la philosophie russe (positivisme, idéalisme, mysticisme chrétien), Grot permit l'émergence de la renaissance philosophique religieuse russe du début du XXe siècle. Sa figure illustre l'importance des médiateurs institutionnels dans la vie intellectuelle : ceux qui créent les conditions du dialogue sans nécessairement dominer le débat.&lt;/p&gt;" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" display="https://www.laphilo.fr/pho/ngrot-mini.webp" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" display="https://www.laphilo.fr/photo/ngrot.webp" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" display="https://www.laphilo.fr/pho/vsoloviev-mini.webp" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" display="https://www.laphilo.fr/pho/nkorkunov-mini.webp" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" display="https://www.laphilo.fr/photo/nkorkunov.webp" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" display="https://www.laphilo.fr/pho/vsoloviev-mini.webp" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" display="https://www.laphilo.fr/pho/nkorkunov-mini.webp" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" display="https://www.laphilo.fr/photo/nkorkunov.webp" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" display="https://www.laphilo.fr/pho/llopatine-mini.webp" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" display="https://www.laphilo.fr/pho/iannenski-mini.webp" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" display="https://www.laphilo.fr/photo/iannenski.webp" r:id="rId87"/>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -3498,15 +3498,15 @@
       </c>
     </row>
     <row r="53" ht="288.05" customHeight="1" s="20">
-      <c r="A53" s="18" t="n">
-        <v>1856</v>
+      <c r="A53" s="18">
+        <v>1855</v>
       </c>
       <c r="B53" s="18" t="n">
         <v>1909</v>
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>1856 – 1909</t>
+          <t xml:space="preserve">1855 – 1909</t>
         </is>
       </c>
       <c r="D53" s="18" t="inlineStr">

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6224,6 +6224,118 @@
       <c r="P99" t="inlineStr">
         <is>
           <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="163.5" customHeight="1" s="20">
+      <c r="A100" s="18">
+        <v>1879</v>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1937</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1879 – 1937</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gustav SPETH</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gustav_Chpet" title=" Wikipedia"&gt;Gustav SPETH&lt;/a&gt; est un philosophe, linguiste et traducteur russe, appelé aussi Chpet d’après la prononciation russe de son nom. Né à Kiev en 1879, il étudie la philosophie dans sa ville, puis enseigne dans des lycées, où il a pour élève la future poétesse Anna Akhmatova. Installé à Moscou en 1907, il part en 1912 à Göttingen suivre les cours d’Edmund Husserl. Il devient ensuite professeur à l’université de Moscou, puis vice-président de l’Académie d’État des sciences de l’art.&lt;/p&gt; &lt;p&gt;Dans &lt;em&gt;Phénomène et sens&lt;/em&gt; (1914), il est le premier à présenter et à discuter en Russie la &lt;a href="https://fr.wikipedia.org/wiki/Ph%C3%A9nom%C3%A9nologie_%28philosophie%29" title=" Wikipedia"&gt;phénoménologie&lt;/a&gt; de Husserl. Il s’en sépare pourtant sur un point : le sens ne naît pas dans une conscience isolée, il est toujours pris dans le langage, la culture et l’histoire. Il fonde ainsi une philosophie du sens, qui accorde une place centrale à l’interprétation : il écrit l’une des premières études sur l’histoire de l’herméneutique et réfléchit sur la « forme interne du mot ». Il travaille aussi sur l’esthétique, la psychologie des peuples et l’histoire de la philosophie russe, qu’il juge sévèrement.&lt;/p&gt; &lt;p&gt;Sous le régime soviétique, il est écarté de l’enseignement. Il se consacre alors à la traduction, notamment de Shakespeare, de Byron et de la &lt;em&gt;Phénoménologie de l’esprit&lt;/em&gt; de Hegel. Arrêté en 1935, exilé en Sibérie, il est fusillé à Tomsk en novembre 1937, pendant la Grande Terreur. Son œuvre, longtemps oubliée, a été redécouverte à la fin du XXe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H100" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/speth-mini.webp</t>
+        </is>
+      </c>
+      <c r="J100" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; langage ; esthetique</t>
+        </is>
+      </c>
+      <c r="K100" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie ; Herméneutique</t>
+        </is>
+      </c>
+      <c r="L100" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe russe, introducteur de la phénoménologie de Husserl en Russie, fusillé pendant la Grande Terreur.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O100"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="163.5" customHeight="1" s="20">
+      <c r="A101" s="18">
+        <v>1930</v>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1930 – 1990</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merab MAMARDACHVILI</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Merab_Mamardachvili" title=" Wikipedia"&gt;Merab MAMARDACHVILI&lt;/a&gt; est un philosophe géorgien de l’époque soviétique. Né à Gori en 1930, il étudie la philosophie à l’université de Moscou. Il travaille à Prague pour une revue communiste internationale, puis à Moscou pour la grande revue &lt;em&gt;Questions de philosophie&lt;/em&gt;, et enseigne dans plusieurs instituts. Jugé trop indépendant, il est écarté de Moscou et s’installe en 1980 à Tbilissi, où il enseigne à l’université. Il meurt d’une crise cardiaque à l’aéroport de Moscou en 1990.&lt;/p&gt; &lt;p&gt;Il écrit peu et pense surtout en parlant. Ses cours, enregistrés par ses étudiants et publiés après sa mort, attirent des foules immenses, à Moscou comme à Tbilissi : des &lt;em&gt;Méditations cartésiennes&lt;/em&gt;, des leçons sur Kant ou sur Proust. Au cœur de sa pensée se trouve la conscience. Penser n’est pas un état naturel, mais un événement rare, qui exige un effort : il faut sans cesse se remettre en question pour accéder à la vérité, qui ne peut être donnée par personne. Avec Descartes, il fait du « je pense » l’acte de liberté par excellence, et lit Proust comme une recherche de soi.&lt;/p&gt; &lt;p&gt;Dans un pays où la pensée officielle était imposée par le parti, sa parole libre fit de lui une figure morale. À la fin de sa vie, il s’oppose au nationalisme géorgien : « Si mon peuple choisit cette voie, je serai contre mon peuple », car la vérité passe avant la patrie. Il a entretenu des liens étroits avec la philosophie française, et un recueil d’entretiens, &lt;em&gt;La Pensée empêchée&lt;/em&gt;, a paru à Paris en 1991.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mamardachvili-mini.webp</t>
+        </is>
+      </c>
+      <c r="J101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
+        </is>
+      </c>
+      <c r="K101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phénoménologie</t>
+        </is>
+      </c>
+      <c r="L101" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe géorgien, penseur de la conscience et de l’effort de penser, figure de la liberté intellectuelle en URSS.</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O101"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géorgienne</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -6336,6 +6336,118 @@
       <c r="P101" t="inlineStr">
         <is>
           <t xml:space="preserve">Géorgienne</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="163.5" customHeight="1" s="20">
+      <c r="A102" s="18">
+        <v>1886</v>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1951</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1886 – 1951</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Georges FEDOTOV</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Georgy_Fedotov" title=" Wikipedia (en)"&gt;Georges FEDOTOV&lt;/a&gt; est un historien, philosophe religieux et essayiste russe. Né à Saratov en 1886, il milite d’abord dans le mouvement social-démocrate, ce qui lui vaut d’être arrêté et exilé. Il étudie l’histoire du Moyen Âge à Saint-Pétersbourg, se tourne vers le christianisme orthodoxe et enseigne à l’université de Saratov après la révolution. En 1925, il quitte la Russie soviétique pour Paris, où il enseigne à l’Institut de théologie orthodoxe Saint-Serge. Menacé par la guerre, il part en 1940 pour les États-Unis et enseigne à New York jusqu’à sa mort en 1951.&lt;/p&gt; &lt;p&gt;Historien de la spiritualité russe, il étudie les saints de l’ancienne Russie et la « mentalité religieuse russe », à laquelle il consacre un grand livre en anglais. Il y met en lumière une sainteté de l’humilité et de la compassion, qui imite l’abaissement du Christ, comme celle des princes Boris et Gleb, qui acceptèrent la mort sans se défendre. Il étudie aussi le rôle des saints fous en Christ et des moines dans la culture russe.&lt;/p&gt; &lt;p&gt;Avec d’autres émigrés, comme Fédor Stepoun, il dirige à Paris la revue &lt;em&gt;La Cité nouvelle&lt;/em&gt; (1931-1939), qui défend une démocratie chrétienne, attentive à la justice sociale, et combat aussi bien le communisme que le fascisme. Dans ses essais sur la Russie et la liberté, il cherche pourquoi son pays a si souvent sacrifié la liberté à la puissance de l’État, et espère une Russie libre et ouverte sur l’Europe. Il s’inscrit dans la tradition de la pensée religieuse russe.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H102" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fedotov-mini.webp</t>
+        </is>
+      </c>
+      <c r="J102" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; politique</t>
+        </is>
+      </c>
+      <c r="K102" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme ; Personnalisme</t>
+        </is>
+      </c>
+      <c r="L102" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">historien et penseur religieux russe de l’émigration, défenseur d’une démocratie chrétienne contre les totalitarismes.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O102"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="163.5" customHeight="1" s="20">
+      <c r="A103" s="18">
+        <v>1882</v>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1952</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1882 – 1952</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lev KARSAVINE</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Lev_Karsavin" title=" Wikipedia (en)"&gt;Lev KARSAVINE&lt;/a&gt; est un philosophe religieux, historien et poète russe. Né à Saint-Pétersbourg en 1882, frère de la célèbre danseuse étoile Tamara Karsavina, il devient un grand spécialiste de la religiosité de l’Italie médiévale et professeur à l’université de Petrograd. En 1922, il fait partie des intellectuels expulsés de Russie par les bolcheviks sur les « bateaux des philosophes », avec Berdiaev et Boulgakov. À Berlin puis à Paris, il devient l’un des penseurs du mouvement eurasiste, qui voit dans la Russie une civilisation propre, ni européenne ni asiatique.&lt;/p&gt; &lt;p&gt;Dans la lignée de Soloviev, il développe une philosophie de l’« unitotalité » : Dieu et le monde forment une unité vivante, où chaque être est une manière singulière d’exprimer le tout. Dans &lt;em&gt;De la personne&lt;/em&gt; (1929), il élabore la notion de « personne symphonique » : non seulement les individus, mais aussi les familles, les peuples, l’Église ou l’humanité sont des personnes, dont les membres s’accordent comme les voix d’un chœur. Toute personne vit en passant par la mort pour ressusciter, à l’image du Christ.&lt;/p&gt; &lt;p&gt;En 1928, il s’installe en Lituanie, où il enseigne à l’université de Kaunas, puis de Vilnius, et écrit en lituanien une grande histoire de la culture européenne. Après l’annexion soviétique, il est arrêté en 1949 et envoyé dans un camp du Grand Nord, à Abez, où il continue d’écrire des poèmes et des traités philosophiques. Il y meurt de la tuberculose en 1952. Il est rattaché au courant de l’&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;eurasisme&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/karsavine-mini.webp</t>
+        </is>
+      </c>
+      <c r="J103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spiritualisme ; Eurasisme</t>
+        </is>
+      </c>
+      <c r="L103" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe religieux et historien russe, penseur de l’unitotalité et de la « personne symphonique », mort au Goulag.</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O103"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.25" customWidth="1" style="18" min="1" max="1"/>
@@ -1272,6 +1272,16 @@
           <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fiodor_Tiouttchev"  title=" Wikipedia"&gt;Fiodor TIOUTTCHEV&lt;/a&gt; était un poète lyrique et penseur politique russe, l'une des grandes voix de la poésie russe du XIXe siècle et un théoricien du panslavisme. Diplomate au service de l'Empire russe à Munich pendant vingt ans, il fut profondément marqué par la philosophie allemande romantique — Schelling fut son ami personnel — et par les débats politiques européens. &lt;a href="http://henri-abril.fr/fiodor-tiouttchev"  title="Henri Abril"&gt; Ses poèmes métaphysiques &lt;/a&gt; et cosmiques, d'une profondeur et d'une densité exceptionnelles, en font l'un des plus grands poètes de la langue russe avec Pouchkine et Lermontov.&lt;/p&gt;&lt;p&gt;Sa philosophie se manifeste avant tout dans sa poésie. Ses poèmes métaphysiques explorent le chaos primordial (Chaos) comme fondement obscur et vital de toute existence, la nuit cosmique comme vérité plus profonde que le jour de la raison, et le silence comme seule réponse adéquate aux questions dernières. Son célèbre quatrain — « La Russie ne peut être comprise par la raison, ni mesurée par l'aune commune, / Elle a sa propre stature particulière — / En la Russie on ne peut que croire. » (1866) — est devenu l'un des énoncés les plus célèbres de la pensée nationale russe.&lt;/p&gt;&lt;p&gt;Ses écrits politiques en prose française — &lt;em&gt;La Russie et la Révolution&lt;/em&gt; (1848), &lt;em&gt;La question romaine et la papauté&lt;/em&gt; (1849), &lt;em&gt;La Russie et l'Occident&lt;/em&gt; (inachevé) — développent une vision géopolitique panslave : l'Europe est en déclin, minée par la révolution et le protestantisme, tandis que la Russie est destinée à constituer autour d'elle un grand empire orthodoxe-slave couvrant de Constantinople à Vladivostok. Cette vision géopolitique, quoique romantique et irréaliste, exerça une influence durable sur le nationalisme russe. Sa combinaison unique de profondeur lyrique et de pensée politique en fait une figure à part dans la philosophie russe.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gvyDPYEIs4o</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Le globe terrestre - Fiodor Tiouttchev" par Relaxation Ici et Là</t>
+        </is>
+      </c>
       <c r="H14" s="19" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/ftiouttchev-mini.webp</t>
@@ -5731,6 +5741,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Mikhail_Lifshitz" title=" Wikipedia"&gt;Mikhaïl LIFSHITZ&lt;/a&gt; était un philosophe, esthéticien et critique d'art marxiste soviétique, l'un des penseurs les plus indépendants et les plus courageux de la philosophie soviétique du XXe siècle. Collaborateur et ami de György Lukács dans les années 1930, il développa avec lui une esthétique marxiste fondée sur l'idéal du réalisme classique contre le formalisme moderniste. Ses travaux sur Marx et l'art, sur Hegel et l'esthétique, et sur la théorie de la connaissance constituent des contributions importantes au marxisme critique.&lt;/p&gt;&lt;p&gt; &lt;a href="https://www.goodreads.com/author/show/7111845.Mikhail_Lifshitz"  title="Lifshitz par goodreads"&gt;Sa philosophie esthétique &lt;/a&gt; s'oppose à la fois au formalisme abstrait (l'art pour l'art) et au réalisme socialiste bureaucratique. S'appuyant sur une lecture attentive des textes de Marx et d'Engels sur l'art, il développe une théorie de la mimesis — la représentation fidèle de la réalité dans sa richesse et ses contradictions — comme fondement de toute grande création artistique. Pour lui, les grands artistes (Homère, Shakespeare, Goethe, Tolstoï) ont su saisir la totalité vivante de leur époque à travers des images concrètes, et c'est cette richesse concrète qui fait la valeur éternelle de leur œuvre.&lt;/p&gt;&lt;p&gt;Son courage intellectuel se manifesta dans sa résistance aux dérives dogmatiques  &lt;a href="https://fr.wikipedia.org/wiki/Jdanovisme_artistique"  title="jdanovisme artistique par wikipedia"&gt;du jdanovisme&lt;/a&gt;, qu'il critiqua avec une ironie mordante sous couvert de fidélité au marxisme classique. Ses travaux sur Lénine et la dialectique, et sa polémique avec les courants structuralistes et sémiotiques des années 1960-1970, témoignent d'une pensée marxiste indépendante et rigoureuse. Il représente le meilleur de l'héritage critique du marxisme soviétique, en rupture avec ses simplifications dogmatiques.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iggGNWeOBik</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Breve esbozo biográfico de Mijaíl Lifshitz - por Manuel Samaja" par Cursos de pensamiento dialéctico</t>
+        </is>
+      </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/mlifshitz-mini.webp</t>
@@ -6190,6 +6210,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roman_Jakobson" title=" Wikipedia"&gt;Roman JAKOBSON&lt;/a&gt; est un linguiste et théoricien de la littérature russe, puis américain, l’un des fondateurs du &lt;a href="https://fr.wikipedia.org/wiki/Structuralisme" title=" Wikipedia"&gt;structuralisme&lt;/a&gt;. Né à Moscou en 1896 dans une famille juive aisée, il fonde en 1915 le Cercle linguistique de Moscou et participe au formalisme russe, qui étudie la littérature à partir de ce qui fait la spécificité d’un texte poétique. Ami des poètes futuristes, comme Maïakovski et Khlebnikov, il s’installe en 1920 en Tchécoslovaquie, où il soutient sa thèse et enseigne à l’université de Brno.&lt;/p&gt; &lt;p&gt;En 1926, il fonde avec Nikolaï Troubetskoï le Cercle linguistique de Prague. Prolongeant Saussure, il fonde la phonologie : une langue n’est pas une collection de sons, mais un système d’oppositions, où chaque son se définit par ce qui le distingue des autres. Fuyant le nazisme en 1939, il passe par la Scandinavie avant de gagner New York en 1941. Il y rencontre &lt;a href="https://fr.wikipedia.org/wiki/Claude_L%C3%A9vi-Strauss" title=" Wikipedia"&gt;Claude Lévi-Strauss&lt;/a&gt;, à qui il fait découvrir la linguistique structurale : c’est de cette rencontre que naît l’anthropologie structurale, puis tout le mouvement structuraliste en France.&lt;/p&gt; &lt;p&gt;Professeur à Harvard et au MIT, il distingue en 1960 six fonctions du langage, selon que le message est tourné vers le monde dont il parle, vers celui qui parle, vers celui qui écoute, vers le contact, vers le code lui-même ou vers sa propre forme, ce qui définit la fonction poétique. Il montre aussi que la métaphore et la métonymie sont les deux grands pôles du langage, que l’aphasie peut toucher séparément. Il meurt à Cambridge, dans le Massachusetts, en 1982.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">f6zR9wyGEx4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Roman Jakobson et Tzevtan Todorov - Regards croisés sur l'apport linguistique de Roman Jakobson" par Artesquieu</t>
+        </is>
+      </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/jakobson-mini.webp</t>
@@ -6446,6 +6476,62 @@
       </c>
       <c r="O103"/>
       <c r="P103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Russe</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="163.5" customHeight="1" s="20">
+      <c r="A104" s="18">
+        <v>1819</v>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1876</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1819 – 1876</t>
+        </is>
+      </c>
+      <c r="D104" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iouri SAMARINE</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iouri_Samarine" title=" Wikipedia"&gt;Iouri SAMARINE&lt;/a&gt; est un philosophe, publiciste et homme public russe, l’un des principaux penseurs slavophiles. Né à Saint-Pétersbourg en 1819 dans une famille de la haute noblesse, il étudie à l’université de Moscou et se passionne d’abord pour Hegel. Sous l’influence d’Alexis Khomiakov, il se tourne vers l’orthodoxie et consacre sa thèse à deux théologiens russes du XVIIIe siècle, Stefan Iavorski et Théophane Prokopovitch, l’un proche du catholicisme, l’autre du protestantisme.&lt;/p&gt; &lt;p&gt;Fonctionnaire à Riga, il critique, dans des &lt;em&gt;Lettres de Riga&lt;/em&gt; (1849), les privilèges de la noblesse allemande des provinces baltes, ce qui lui vaut d’être enfermé quelques jours dans la forteresse Pierre-et-Paul. Défenseur de la commune paysanne, qu’il voit comme une forme russe de vie collective, il milite pour l’abolition du servage et participe de près à la préparation de la réforme de 1861. En 1864, il contribue en Pologne à la réforme qui donne la terre aux paysans. Dans &lt;em&gt;Les Confins de la Russie&lt;/em&gt;, il s’en prend de nouveau aux privilèges des Allemands baltes, qui freinent selon lui l’unité de l’Empire.&lt;/p&gt; &lt;p&gt;Ami et disciple de Khomiakov, il publie ses écrits théologiques, interdits en Russie, et leur donne une préface célèbre : la vérité ne se découvre pas par la raison seule, mais dans la vie de foi et l’amour de l’Église. Il défend une foi vivante contre le rationalisme. Il meurt à Berlin en 1876. Il est une figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/Slavophilie" title=" Wikipedia"&gt;slavophilisme&lt;/a&gt;.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/samarine-mini.webp</t>
+        </is>
+      </c>
+      <c r="J104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">politique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="K104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slavophilisme</t>
+        </is>
+      </c>
+      <c r="L104" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penseur slavophile russe, artisan de l’abolition du servage et éditeur de Khomiakov.</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">russe</t>
+        </is>
+      </c>
+      <c r="O104"/>
+      <c r="P104" t="inlineStr">
         <is>
           <t xml:space="preserve">Russe</t>
         </is>

--- a/data/frise-philosophes-russes.xlsx
+++ b/data/frise-philosophes-russes.xlsx
@@ -6315,46 +6315,46 @@
     </row>
     <row r="101" ht="163.5" customHeight="1" s="20">
       <c r="A101" s="18">
-        <v>1930</v>
+        <v>1886</v>
       </c>
       <c r="B101" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990</t>
+          <t xml:space="preserve">1951</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930 – 1990</t>
+          <t xml:space="preserve">1886 – 1951</t>
         </is>
       </c>
       <c r="D101" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merab MAMARDACHVILI</t>
+          <t xml:space="preserve">Georges FEDOTOV</t>
         </is>
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Merab_Mamardachvili" title=" Wikipedia"&gt;Merab MAMARDACHVILI&lt;/a&gt; est un philosophe géorgien de l’époque soviétique. Né à Gori en 1930, il étudie la philosophie à l’université de Moscou. Il travaille à Prague pour une revue communiste internationale, puis à Moscou pour la grande revue &lt;em&gt;Questions de philosophie&lt;/em&gt;, et enseigne dans plusieurs instituts. Jugé trop indépendant, il est écarté de Moscou et s’installe en 1980 à Tbilissi, où il enseigne à l’université. Il meurt d’une crise cardiaque à l’aéroport de Moscou en 1990.&lt;/p&gt; &lt;p&gt;Il écrit peu et pense surtout en parlant. Ses cours, enregistrés par ses étudiants et publiés après sa mort, attirent des foules immenses, à Moscou comme à Tbilissi : des &lt;em&gt;Méditations cartésiennes&lt;/em&gt;, des leçons sur Kant ou sur Proust. Au cœur de sa pensée se trouve la conscience. Penser n’est pas un état naturel, mais un événement rare, qui exige un effort : il faut sans cesse se remettre en question pour accéder à la vérité, qui ne peut être donnée par personne. Avec Descartes, il fait du « je pense » l’acte de liberté par excellence, et lit Proust comme une recherche de soi.&lt;/p&gt; &lt;p&gt;Dans un pays où la pensée officielle était imposée par le parti, sa parole libre fit de lui une figure morale. À la fin de sa vie, il s’oppose au nationalisme géorgien : « Si mon peuple choisit cette voie, je serai contre mon peuple », car la vérité passe avant la patrie. Il a entretenu des liens étroits avec la philosophie française, et un recueil d’entretiens, &lt;em&gt;La Pensée empêchée&lt;/em&gt;, a paru à Paris en 1991.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Georgy_Fedotov" title=" Wikipedia (en)"&gt;Georges FEDOTOV&lt;/a&gt; est un historien, philosophe religieux et essayiste russe. Né à Saratov en 1886, il milite d’abord dans le mouvement social-démocrate, ce qui lui vaut d’être arrêté et exilé. Il étudie l’histoire du Moyen Âge à Saint-Pétersbourg, se tourne vers le christianisme orthodoxe et enseigne à l’université de Saratov après la révolution. En 1925, il quitte la Russie soviétique pour Paris, où il enseigne à l’Institut de théologie orthodoxe Saint-Serge. Menacé par la guerre, il part en 1940 pour les États-Unis et enseigne à New York jusqu’à sa mort en 1951.&lt;/p&gt; &lt;p&gt;Historien de la spiritualité russe, il étudie les saints de l’ancienne Russie et la « mentalité religieuse russe », à laquelle il consacre un grand livre en anglais. Il y met en lumière une sainteté de l’humilité et de la compassion, qui imite l’abaissement du Christ, comme celle des princes Boris et Gleb, qui acceptèrent la mort sans se défendre. Il étudie aussi le rôle des saints fous en Christ et des moines dans la culture russe.&lt;/p&gt; &lt;p&gt;Avec d’autres émigrés, comme Fédor Stepoun, il dirige à Paris la revue &lt;em&gt;La Cité nouvelle&lt;/em&gt; (1931-1939), qui défend une démocratie chrétienne, attentive à la justice sociale, et combat aussi bien le communisme que le fascisme. Dans ses essais sur la Russie et la liberté, il cherche pourquoi son pays a si souvent sacrifié la liberté à la puissance de l’État, et espère une Russie libre et ouverte sur l’Europe. Il s’inscrit dans la tradition de la pensée religieuse russe.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/mamardachvili-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/fedotov-mini.webp</t>
         </is>
       </c>
       <c r="J101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; epistemologie</t>
+          <t xml:space="preserve">spiritualite ; politique</t>
         </is>
       </c>
       <c r="K101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phénoménologie</t>
+          <t xml:space="preserve">Spiritualisme ; Personnalisme</t>
         </is>
       </c>
       <c r="L101" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe géorgien, penseur de la conscience et de l’effort de penser, figure de la liberté intellectuelle en URSS.</t>
+          <t xml:space="preserve">historien et penseur religieux russe de l’émigration, défenseur d’une démocratie chrétienne contre les totalitarismes.</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -6365,52 +6365,52 @@
       <c r="O101"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Géorgienne</t>
+          <t xml:space="preserve">Russe</t>
         </is>
       </c>
     </row>
     <row r="102" ht="163.5" customHeight="1" s="20">
       <c r="A102" s="18">
-        <v>1886</v>
+        <v>1882</v>
       </c>
       <c r="B102" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1951</t>
+          <t xml:space="preserve">1952</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886 – 1951</t>
+          <t xml:space="preserve">1882 – 1952</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Georges FEDOTOV</t>
+          <t xml:space="preserve">Lev KARSAVINE</t>
         </is>
       </c>
       <c r="E102" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Georgy_Fedotov" title=" Wikipedia (en)"&gt;Georges FEDOTOV&lt;/a&gt; est un historien, philosophe religieux et essayiste russe. Né à Saratov en 1886, il milite d’abord dans le mouvement social-démocrate, ce qui lui vaut d’être arrêté et exilé. Il étudie l’histoire du Moyen Âge à Saint-Pétersbourg, se tourne vers le christianisme orthodoxe et enseigne à l’université de Saratov après la révolution. En 1925, il quitte la Russie soviétique pour Paris, où il enseigne à l’Institut de théologie orthodoxe Saint-Serge. Menacé par la guerre, il part en 1940 pour les États-Unis et enseigne à New York jusqu’à sa mort en 1951.&lt;/p&gt; &lt;p&gt;Historien de la spiritualité russe, il étudie les saints de l’ancienne Russie et la « mentalité religieuse russe », à laquelle il consacre un grand livre en anglais. Il y met en lumière une sainteté de l’humilité et de la compassion, qui imite l’abaissement du Christ, comme celle des princes Boris et Gleb, qui acceptèrent la mort sans se défendre. Il étudie aussi le rôle des saints fous en Christ et des moines dans la culture russe.&lt;/p&gt; &lt;p&gt;Avec d’autres émigrés, comme Fédor Stepoun, il dirige à Paris la revue &lt;em&gt;La Cité nouvelle&lt;/em&gt; (1931-1939), qui défend une démocratie chrétienne, attentive à la justice sociale, et combat aussi bien le communisme que le fascisme. Dans ses essais sur la Russie et la liberté, il cherche pourquoi son pays a si souvent sacrifié la liberté à la puissance de l’État, et espère une Russie libre et ouverte sur l’Europe. Il s’inscrit dans la tradition de la pensée religieuse russe.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Lev_Karsavin" title=" Wikipedia (en)"&gt;Lev KARSAVINE&lt;/a&gt; est un philosophe religieux, historien et poète russe. Né à Saint-Pétersbourg en 1882, frère de la célèbre danseuse étoile Tamara Karsavina, il devient un grand spécialiste de la religiosité de l’Italie médiévale et professeur à l’université de Petrograd. En 1922, il fait partie des intellectuels expulsés de Russie par les bolcheviks sur les « bateaux des philosophes », avec Berdiaev et Boulgakov. À Berlin puis à Paris, il devient l’un des penseurs du mouvement eurasiste, qui voit dans la Russie une civilisation propre, ni européenne ni asiatique.&lt;/p&gt; &lt;p&gt;Dans la lignée de Soloviev, il développe une philosophie de l’« unitotalité » : Dieu et le monde forment une unité vivante, où chaque être est une manière singulière d’exprimer le tout. Dans &lt;em&gt;De la personne&lt;/em&gt; (1929), il élabore la notion de « personne symphonique » : non seulement les individus, mais aussi les familles, les peuples, l’Église ou l’humanité sont des personnes, dont les membres s’accordent comme les voix d’un chœur. Toute personne vit en passant par la mort pour ressusciter, à l’image du Christ.&lt;/p&gt; &lt;p&gt;En 1928, il s’installe en Lituanie, où il enseigne à l’université de Kaunas, puis de Vilnius, et écrit en lituanien une grande histoire de la culture européenne. Après l’annexion soviétique, il est arrêté en 1949 et envoyé dans un camp du Grand Nord, à Abez, où il continue d’écrire des poèmes et des traités philosophiques. Il y meurt de la tuberculose en 1952. Il est rattaché au courant de l’&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;eurasisme&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/fedotov-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/karsavine-mini.webp</t>
         </is>
       </c>
       <c r="J102" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">spiritualite ; politique</t>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
         </is>
       </c>
       <c r="K102" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Personnalisme</t>
+          <t xml:space="preserve">Spiritualisme ; Eurasisme</t>
         </is>
       </c>
       <c r="L102" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">historien et penseur religieux russe de l’émigration, défenseur d’une démocratie chrétienne contre les totalitarismes.</t>
+          <t xml:space="preserve">philosophe religieux et historien russe, penseur de l’unitotalité et de la « personne symphonique », mort au Goulag.</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -6427,46 +6427,46 @@
     </row>
     <row r="103" ht="163.5" customHeight="1" s="20">
       <c r="A103" s="18">
-        <v>1882</v>
+        <v>1819</v>
       </c>
       <c r="B103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1952</t>
+          <t xml:space="preserve">1876</t>
         </is>
       </c>
       <c r="C103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882 – 1952</t>
+          <t xml:space="preserve">1819 – 1876</t>
         </is>
       </c>
       <c r="D103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lev KARSAVINE</t>
+          <t xml:space="preserve">Iouri SAMARINE</t>
         </is>
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Lev_Karsavin" title=" Wikipedia (en)"&gt;Lev KARSAVINE&lt;/a&gt; est un philosophe religieux, historien et poète russe. Né à Saint-Pétersbourg en 1882, frère de la célèbre danseuse étoile Tamara Karsavina, il devient un grand spécialiste de la religiosité de l’Italie médiévale et professeur à l’université de Petrograd. En 1922, il fait partie des intellectuels expulsés de Russie par les bolcheviks sur les « bateaux des philosophes », avec Berdiaev et Boulgakov. À Berlin puis à Paris, il devient l’un des penseurs du mouvement eurasiste, qui voit dans la Russie une civilisation propre, ni européenne ni asiatique.&lt;/p&gt; &lt;p&gt;Dans la lignée de Soloviev, il développe une philosophie de l’« unitotalité » : Dieu et le monde forment une unité vivante, où chaque être est une manière singulière d’exprimer le tout. Dans &lt;em&gt;De la personne&lt;/em&gt; (1929), il élabore la notion de « personne symphonique » : non seulement les individus, mais aussi les familles, les peuples, l’Église ou l’humanité sont des personnes, dont les membres s’accordent comme les voix d’un chœur. Toute personne vit en passant par la mort pour ressusciter, à l’image du Christ.&lt;/p&gt; &lt;p&gt;En 1928, il s’installe en Lituanie, où il enseigne à l’université de Kaunas, puis de Vilnius, et écrit en lituanien une grande histoire de la culture européenne. Après l’annexion soviétique, il est arrêté en 1949 et envoyé dans un camp du Grand Nord, à Abez, où il continue d’écrire des poèmes et des traités philosophiques. Il y meurt de la tuberculose en 1952. Il est rattaché au courant de l’&lt;a href="https://fr.wikipedia.org/wiki/Eurasisme" title=" Wikipedia"&gt;eurasisme&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iouri_Samarine" title=" Wikipedia"&gt;Iouri SAMARINE&lt;/a&gt; est un philosophe, publiciste et homme public russe, l’un des principaux penseurs slavophiles. Né à Saint-Pétersbourg en 1819 dans une famille de la haute noblesse, il étudie à l’université de Moscou et se passionne d’abord pour Hegel. Sous l’influence d’Alexis Khomiakov, il se tourne vers l’orthodoxie et consacre sa thèse à deux théologiens russes du XVIIIe siècle, Stefan Iavorski et Théophane Prokopovitch, l’un proche du catholicisme, l’autre du protestantisme.&lt;/p&gt; &lt;p&gt;Fonctionnaire à Riga, il critique, dans des &lt;em&gt;Lettres de Riga&lt;/em&gt; (1849), les privilèges de la noblesse allemande des provinces baltes, ce qui lui vaut d’être enfermé quelques jours dans la forteresse Pierre-et-Paul. Défenseur de la commune paysanne, qu’il voit comme une forme russe de vie collective, il milite pour l’abolition du servage et participe de près à la préparation de la réforme de 1861. En 1864, il contribue en Pologne à la réforme qui donne la terre aux paysans. Dans &lt;em&gt;Les Confins de la Russie&lt;/em&gt;, il s’en prend de nouveau aux privilèges des Allemands baltes, qui freinent selon lui l’unité de l’Empire.&lt;/p&gt; &lt;p&gt;Ami et disciple de Khomiakov, il publie ses écrits théologiques, interdits en Russie, et leur donne une préface célèbre : la vérité ne se découvre pas par la raison seule, mais dans la vie de foi et l’amour de l’Église. Il défend une foi vivante contre le rationalisme. Il meurt à Berlin en 1876. Il est une figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/Slavophilie" title=" Wikipedia"&gt;slavophilisme&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/karsavine-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/samarine-mini.webp</t>
         </is>
       </c>
       <c r="J103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">metaphysique ; spiritualite</t>
+          <t xml:space="preserve">politique ; spiritualite</t>
         </is>
       </c>
       <c r="K103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spiritualisme ; Eurasisme</t>
+          <t xml:space="preserve">Slavophilisme</t>
         </is>
       </c>
       <c r="L103" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">philosophe religieux et historien russe, penseur de l’unitotalité et de la « personne symphonique », mort au Goulag.</t>
+          <t xml:space="preserve">penseur slavophile russe, artisan de l’abolition du servage et éditeur de Khomiakov.</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -6483,46 +6483,56 @@
     </row>
     <row r="104" ht="163.5" customHeight="1" s="20">
       <c r="A104" s="18">
-        <v>1819</v>
+        <v>1930</v>
       </c>
       <c r="B104" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1876</t>
+          <t xml:space="preserve">1990</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819 – 1876</t>
+          <t xml:space="preserve">1930 – 1990</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iouri SAMARINE</t>
+          <t xml:space="preserve">Merab MAMARDACHVILI</t>
         </is>
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Iouri_Samarine" title=" Wikipedia"&gt;Iouri SAMARINE&lt;/a&gt; est un philosophe, publiciste et homme public russe, l’un des principaux penseurs slavophiles. Né à Saint-Pétersbourg en 1819 dans une famille de la haute noblesse, il étudie à l’université de Moscou et se passionne d’abord pour Hegel. Sous l’influence d’Alexis Khomiakov, il se tourne vers l’orthodoxie et consacre sa thèse à deux théologiens russes du XVIIIe siècle, Stefan Iavorski et Théophane Prokopovitch, l’un proche du catholicisme, l’autre du protestantisme.&lt;/p&gt; &lt;p&gt;Fonctionnaire à Riga, il critique, dans des &lt;em&gt;Lettres de Riga&lt;/em&gt; (1849), les privilèges de la noblesse allemande des provinces baltes, ce qui lui vaut d’être enfermé quelques jours dans la forteresse Pierre-et-Paul. Défenseur de la commune paysanne, qu’il voit comme une forme russe de vie collective, il milite pour l’abolition du servage et participe de près à la préparation de la réforme de 1861. En 1864, il contribue en Pologne à la réforme qui donne la terre aux paysans. Dans &lt;em&gt;Les Confins de la Russie&lt;/em&gt;, il s’en prend de nouveau aux privilèges des Allemands baltes, qui freinent selon lui l’unité de l’Empire.&lt;/p&gt; &lt;p&gt;Ami et disciple de Khomiakov, il publie ses écrits théologiques, interdits en Russie, et leur donne une préface célèbre : la vérité ne se découvre pas par la raison seule, mais dans la vie de foi et l’amour de l’Église. Il défend une foi vivante contre le rationalisme. Il meurt à Berlin en 1876. Il est une figure majeure du &lt;a href="https://fr.wikipedia.org/wiki/Slavophilie" title=" Wikipedia"&gt;slavophilisme&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Merab_Mamardachvili" title=" Wikipedia"&gt;Merab MAMARDACHVILI&lt;/a&gt; est un philosophe géorgien de l’époque soviétique. Né à Gori, il étudie la philosophie à l’université de Moscou. Il travaille à Prague pour une revue communiste internationale, puis à Moscou pour la grande revue &lt;em&gt;Questions de philosophie&lt;/em&gt;, et enseigne dans plusieurs instituts. Jugé trop indépendant, il est écarté de Moscou et s’installe en 1980 à Tbilissi, où il enseigne à l’université. Il meurt d’une crise cardiaque à l’aéroport de Moscou en 1990.&lt;/p&gt; &lt;p&gt;Il écrit peu et &lt;a href="https://www.persee.fr/doc/slaoc_1245-2491_2019_num_49_1_1263" title="La notion de philosophie dans l’oeuvre de Mérab Mamardachvili par persée"&gt;pense surtout en parlant&lt;/a&gt;. Ses cours, enregistrés par ses étudiants et publiés après sa mort, attirent des foules immenses, à Moscou comme à Tbilissi : des &lt;em&gt;Méditations cartésiennes&lt;/em&gt;, des leçons sur Kant ou sur Proust. Au cœur de sa pensée se trouve la conscience. Penser n’est pas un état naturel, mais un événement rare, qui exige un effort : il faut sans cesse &lt;a href="https://www.youtube.com/watch?v=DHK-ca58h-I" title="Pensez-vous vraiment ? L'étincelle de Mamardashvili contre nos simulacres. par Meditor Aeterna"&gt;se remettre en question&lt;/a&gt; pour accéder à la vérité, qui ne peut être donnée par personne. Avec Descartes, il fait du « je pense » l’acte de liberté par excellence, et lit Proust comme une recherche de soi.&lt;/p&gt; &lt;p&gt;Dans un pays où la pensée officielle était imposée par le parti, sa parole libre fit de lui une figure morale. À la fin de sa vie, il s’oppose au nationalisme géorgien : « Si mon peuple choisit cette voie, je serai contre mon peuple », car la vérité passe avant la patrie. Il a entretenu des liens étroits avec la philosophie française, et un recueil d’entretiens, &lt;em&gt;La Pensée empêchée&lt;/em&gt;, a paru à Paris en 1991.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1C2Zhz-KgAQ</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Pensez-vous vraiment par vous-même ? (Le secret de Merab Mamardashvili)" par Meditor Aeterna</t>
         </is>
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.laphilo.fr/pho/samarine-mini.webp</t>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/mamardachvili-mini.webp</t>
         </is>
       </c>
       <c r="J104" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">politique ; spiritualite</t>
+          <t xml:space="preserve">metaphysique ; epistemologie</t>
         </is>
       </c>
       <c r="K104" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slavophilisme</t>
+          <t xml:space="preserve">Phénoménologie</t>
         </is>
       </c>
       <c r="L104" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">penseur slavophile russe, artisan de l’abolition du servage et éditeur de Khomiakov.</t>
+          <t xml:space="preserve">philosophe géorgien, penseur de la conscience et de l’effort de penser, figure de la liberté intellectuelle en URSS.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -6533,7 +6543,7 @@
       <c r="O104"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Russe</t>
+          <t xml:space="preserve">Géorgienne</t>
         </is>
       </c>
     </row>
